--- a/04_DESIGN_TABLES/DesignTable_6500_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6500_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM16"/>
+  <dimension ref="A1:BM25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,13 +901,13 @@
         <v>0.53125</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.61343</v>
+        <v>0.61293</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1118,13 +1118,13 @@
         <v>0.22</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1175,26 +1175,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6500-05-05-FG</t>
+          <t>6500-04-06-FG</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.95</v>
+        <v>1.05</v>
       </c>
       <c r="C4" t="n">
-        <v>0.28</v>
+        <v>0.281</v>
       </c>
       <c r="D4" t="n">
-        <v>0.25</v>
+        <v>0.21875</v>
       </c>
       <c r="E4" t="n">
         <v>0.075</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2606</v>
+        <v>0.2608</v>
       </c>
       <c r="G4" t="n">
-        <v>0.213</v>
+        <v>0.182</v>
       </c>
       <c r="H4" t="n">
         <v>0.0795</v>
@@ -1209,85 +1209,85 @@
         <v>37</v>
       </c>
       <c r="L4" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="M4" t="n">
-        <v>0.28</v>
+        <v>0.281</v>
       </c>
       <c r="N4" t="n">
-        <v>0.746</v>
+        <v>0.785</v>
       </c>
       <c r="O4" t="n">
-        <v>0.178</v>
+        <v>0.206</v>
       </c>
       <c r="P4" t="n">
-        <v>0.715</v>
+        <v>0.735</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2912</v>
+        <v>0.3224</v>
       </c>
       <c r="R4" t="n">
         <v>0.145</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3113</v>
+        <v>0.3428</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3826</v>
+        <v>0.3876</v>
       </c>
       <c r="U4" t="n">
-        <v>0.36373</v>
+        <v>0.39722</v>
       </c>
       <c r="V4" t="n">
-        <v>0.25</v>
+        <v>0.28125</v>
       </c>
       <c r="W4" t="n">
-        <v>0.22294</v>
+        <v>0.25118</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2938</v>
+        <v>0.2945</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2675</v>
+        <v>0.2925</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.5901</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.218</v>
+        <v>0.246</v>
       </c>
       <c r="AB4" t="n">
         <v>0.37</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.175</v>
+        <v>0.215</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.63</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3826</v>
+        <v>0.3876</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.23</v>
+        <v>0.172</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.95</v>
+        <v>1.05</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.23</v>
+        <v>0.297</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="AK4" t="n">
         <v>0.05</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.2606</v>
+        <v>0.2608</v>
       </c>
       <c r="AM4" t="n">
         <v>0.02706</v>
@@ -1299,58 +1299,58 @@
         <v>0.05</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.44588</v>
+        <v>0.50236</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.3165</v>
+        <v>0.3197</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.05</v>
+        <v>0.05556</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.22294</v>
+        <v>0.25118</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.25</v>
+        <v>0.28125</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.314</v>
+        <v>0.465</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.28</v>
+        <v>0.281</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.28</v>
+        <v>0.281</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.16166</v>
+        <v>0.16174</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.16166</v>
+        <v>0.16174</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.32332</v>
+        <v>0.32397</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>6500-05-05-FG</t>
+          <t>6500-04-06-FG</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 1/2-20 JIC x 1/2-20 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 7/16-20 JIC x 9/16-18 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -1360,12 +1360,12 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1/2-20 JIC</t>
+          <t>7/16-20 JIC</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>1/2-20 (female 37deg JIC swivel)</t>
+          <t>9/16-18 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1375,49 +1375,49 @@
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-04-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied; 2026-10-09 (left out of batch 15, staged): LEG_M@DRIVE: OMi Items row 1913 L 1 Size = 1.05; LEG_M5@DRIVE: OMi Items row 1913 M 2 Size = 1.25; LEG_M10@DRIVE: OMi Items row 1913 M 1 Size = 0.88; HEXB@HEX: OMi Items row 1913 Nut Hex 1 = 0.688; Y@REF: OMi Items row 1913 Hex Flat = 0.562; D1@BORE: OMi Items row 1913 Side 1 ID = 0.172; D2@BORE: OMi Items row 1913 Side 2 ID = 0.297; THDMAJ_A@DRIVE: 7/16-20 -&gt; 0.4375 (end library); THDMAJ_B@DRIVE: 9/16-18 -&gt; 0.5625 (end library) [user 2026-09-25: OMi dims &gt; Air-Way; user 2026-10-08: no size from Brennan alone -&gt; OMi stands, ASSUMED]; pairing: OMi L 1 = male JIC leg (catalog M), M 2 = swivel-nut face (M6), M 1 = swivel nose / seat (M4), Hex Flat = body hex, Nut Hex 1 = swivel nut hex, Side 1 / 2 ID = bores of ends 1 / 2 (batch-15 pairing, Brennan TFA p34 letters) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs) | leg 2: the corner puck (radius 0.323) reaches 0.009 past the swivel body face (0.314) but stays inside the neck (max 0.077 off the axis vs neck radius 0.178) - as on the Brennan 6502-08-08-FG / 1503-08-08-FG forgings; leg 2 hex arm 0.314 barely clears the corner puck (radius 0.323)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-04-06 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-09 (staged): this part's own sizes from OMi WebsitePartsInfo2026 Items row 1913 - ASSUMED (one source). It was held in batch 15 because the Brennan TFA catalog prints other values for it; under the 2026-10-08 ruling the catalog (= OMi's source) is evidence only and OMi stands. Catalog print for the record: TFA-p034-t01: TUBE O.D. 1/4, B1 SAE 37Deg 7/16-20, B2 SAE 37Deg 9/16-18, B1 DRILL 0.172, B2 DRILL 0.297, M LGTH 1.05, M4 LGTH 0.87, M6 LGTH 1.25, C HEX 0.688, Y FLATS 0.562</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>6500-05-05-FG</t>
+          <t>6500-04-06-FG</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6500-06-04-FG</t>
+          <t>6500-05-05-FG</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.06</v>
+        <v>0.95</v>
       </c>
       <c r="C5" t="n">
-        <v>0.28125</v>
+        <v>0.28</v>
       </c>
       <c r="D5" t="n">
-        <v>0.28125</v>
+        <v>0.25</v>
       </c>
       <c r="E5" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2515</v>
+        <v>0.2606</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2405</v>
+        <v>0.213</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
@@ -1426,148 +1426,148 @@
         <v>37</v>
       </c>
       <c r="L5" t="n">
-        <v>1.24</v>
+        <v>1.06</v>
       </c>
       <c r="M5" t="n">
-        <v>0.28125</v>
+        <v>0.28</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1465</v>
+        <v>0.178</v>
       </c>
       <c r="P5" t="n">
-        <v>0.649</v>
+        <v>0.715</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2574</v>
+        <v>0.2912</v>
       </c>
       <c r="R5" t="n">
-        <v>0.14</v>
+        <v>0.145</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2796</v>
+        <v>0.3113</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3268</v>
+        <v>0.3826</v>
       </c>
       <c r="U5" t="n">
-        <v>0.32447</v>
+        <v>0.36373</v>
       </c>
       <c r="V5" t="n">
-        <v>0.21875</v>
+        <v>0.25</v>
       </c>
       <c r="W5" t="n">
-        <v>0.19169</v>
+        <v>0.22294</v>
       </c>
       <c r="X5" t="n">
-        <v>0.264</v>
+        <v>0.2938</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.235</v>
+        <v>0.2675</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.5243</v>
+        <v>0.5901</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1845</v>
+        <v>0.218</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.145</v>
+        <v>0.175</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3268</v>
+        <v>0.3826</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.297</v>
+        <v>0.23</v>
       </c>
       <c r="AG5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AI5" t="n">
         <v>1.06</v>
       </c>
-      <c r="AH5" t="n">
-        <v>0.172</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.2515</v>
+        <v>0.2606</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.38338</v>
+        <v>0.44588</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.2867</v>
+        <v>0.3165</v>
       </c>
       <c r="AR5" t="n">
         <v>0.05</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.19169</v>
+        <v>0.22294</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.21875</v>
+        <v>0.25</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.24</v>
+        <v>1.06</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.5625</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.504</v>
+        <v>0.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.5625</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.555</v>
+        <v>0.314</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.28125</v>
+        <v>0.28</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.28125</v>
+        <v>0.28</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.16238</v>
+        <v>0.16116</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.16238</v>
+        <v>0.16116</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.32476</v>
+        <v>0.32282</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>6500-06-04-FG</t>
+          <t>6500-05-05-FG</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 9/16-18 JIC x 7/16-20 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 1/2-20 JIC x 1/2-20 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>9/16-18 JIC</t>
+          <t>1/2-20 JIC</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>7/16-20 (female 37deg JIC swivel)</t>
+          <t>1/2-20 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -1592,24 +1592,24 @@
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-06-04 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied; BATCH 15 (2026-10-02, staged): LEG_M@DRIVE: OMi Items!P1915 L 1 Size = 1.06 (table had empty); LEG_M5@DRIVE: OMi Items!O1915 M 2 Size = 1.24 (table had empty); LEG_M10@DRIVE: OMi Items!N1915 M 1 Size = 0.90 (table had empty); HEXB@HEX: OMi Items!V1915 Nut Hex 1 = 0.562 (table had empty); Y@REF: OMi Items!R1915 Hex Flat = 0.562 (table had empty); D1@BORE: OMi Items!S1915 Side 1 ID = 0.297 (table had empty); D2@BORE: OMi Items!X1915 Side 2 ID = 0.172 (table had empty); THDMAJ_A@DRIVE: 9/16-18 -&gt; 0.5625 (dash-correct end library: MS33656J / gen_straight2 JIC); THDMAJ_B@DRIVE: 7/16-20 -&gt; 0.4375 (dash-correct end library: MS33656J / gen_straight2 JIC) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED; batch 15 go-ahead user 2026-10-02 (staged)]; column pairing: OMi L 1 = catalog M (male JIC leg), M 2 = M6 (swivel-nut face; drawn "M5"), M 1 = M4 (swivel nose / seat), Hex Flat = Y FLATS, Nut Hex 1 = C HEX, Side 1 / 2 ID = B1 / B2 DRILL (TFA p34 6500-FG drawing letters; Q-B-SWELB answered by the catalog, 00_DOCS/Brennan_Catalog_2026-10-01.md 3.5 + impact/F1b.json); cross-check: Brennan TFA catalog p34 6500-06-04-FG row = OMi on every cell (rounding only: HEXB@HEX: catalog C HEX 0.563 vs OMi 0.562 - rounding only, OMi kept) - same source as OMi (not a 2nd source); the non-forged Air-Way row of this size is NOT used; the generator MODEL text names the leg columns "Air-Way M5 / M10" - on this row they hold the OMi values above | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-06-04 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-02 (batch 15, staged for review): this -FG part's own dimensions from OMi WebsitePartsInfo2026.xlsx Items row 1915 (= Brennan TFA p34 6500-06-04-FG, one source) - ASSUMED; catalog rounding-only prints: HEXB@HEX: catalog C HEX 0.563 vs OMi 0.562 - rounding only, OMi kept; open, NON-gating: Q-NEW-MS51531NUT (optional routes to VERIFIED only - TaskC_resort.md 3d "never gate building": Q-NEW-MS51531NUT = MS51531D tube-nut hex as a 2nd source for the swivel nut hex) | hex A/F raised from Air-Way 0.562 to 0.5625 (JIC thread major; 2603HX rule)</t>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs) | leg 2: the corner puck (radius 0.323) reaches 0.009 past the swivel body face (0.314) but stays inside the neck (max 0.077 off the axis vs neck radius 0.178) - as on the Brennan 6502-08-08-FG / 1503-08-08-FG forgings; leg 2 hex arm 0.314 barely clears the corner puck (radius 0.323)</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>6500-06-04-FG</t>
+          <t>6500-05-05-FG</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6500-06-06-FG</t>
+          <t>6500-06-04-FG</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1643,76 +1643,76 @@
         <v>37</v>
       </c>
       <c r="L6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M6" t="n">
         <v>0.28125</v>
       </c>
       <c r="N6" t="n">
-        <v>0.785</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.206</v>
+        <v>0.1465</v>
       </c>
       <c r="P6" t="n">
-        <v>0.735</v>
+        <v>0.649</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3224</v>
+        <v>0.2574</v>
       </c>
       <c r="R6" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.19169</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.5243</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.1845</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AC6" t="n">
         <v>0.145</v>
       </c>
-      <c r="S6" t="n">
-        <v>0.3428</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.3876</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.39837</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.28125</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.25118</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.2945</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.2925</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.5953000000000001</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.246</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.215</v>
-      </c>
       <c r="AD6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.3876</v>
+        <v>0.3268</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.3</v>
+        <v>0.297</v>
       </c>
       <c r="AG6" t="n">
         <v>1.06</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.3</v>
+        <v>0.172</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AJ6" t="n">
         <v>0.5625</v>
@@ -1733,22 +1733,22 @@
         <v>0.05556</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.50236</v>
+        <v>0.38338</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.3197</v>
+        <v>0.2867</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.25118</v>
+        <v>0.19169</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AV6" t="n">
         <v>0.5625</v>
@@ -1760,7 +1760,7 @@
         <v>0.5625</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.465</v>
+        <v>0.555</v>
       </c>
       <c r="AZ6" t="n">
         <v>0.28125</v>
@@ -1769,22 +1769,22 @@
         <v>0.28125</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.32476</v>
+        <v>0.32426</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>6500-06-06-FG</t>
+          <t>6500-06-04-FG</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 9/16-18 JIC x 9/16-18 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 9/16-18 JIC x 7/16-20 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>9/16-18 (female 37deg JIC swivel)</t>
+          <t>7/16-20 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -1809,31 +1809,31 @@
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-06-04 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied; BATCH 15 (2026-10-02, staged): LEG_M@DRIVE: OMi Items!P1915 L 1 Size = 1.06 (table had empty); LEG_M5@DRIVE: OMi Items!O1915 M 2 Size = 1.24 (table had empty); LEG_M10@DRIVE: OMi Items!N1915 M 1 Size = 0.90 (table had empty); HEXB@HEX: OMi Items!V1915 Nut Hex 1 = 0.562 (table had empty); Y@REF: OMi Items!R1915 Hex Flat = 0.562 (table had empty); D1@BORE: OMi Items!S1915 Side 1 ID = 0.297 (table had empty); D2@BORE: OMi Items!X1915 Side 2 ID = 0.172 (table had empty); THDMAJ_A@DRIVE: 9/16-18 -&gt; 0.5625 (dash-correct end library: MS33656J / gen_straight2 JIC); THDMAJ_B@DRIVE: 7/16-20 -&gt; 0.4375 (dash-correct end library: MS33656J / gen_straight2 JIC) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED; batch 15 go-ahead user 2026-10-02 (staged)]; column pairing: OMi L 1 = catalog M (male JIC leg), M 2 = M6 (swivel-nut face; drawn "M5"), M 1 = M4 (swivel nose / seat), Hex Flat = Y FLATS, Nut Hex 1 = C HEX, Side 1 / 2 ID = B1 / B2 DRILL (TFA p34 6500-FG drawing letters; Q-B-SWELB answered by the catalog, 00_DOCS/Brennan_Catalog_2026-10-01.md 3.5 + impact/F1b.json); cross-check: Brennan TFA catalog p34 6500-06-04-FG row = OMi on every cell (rounding only: HEXB@HEX: catalog C HEX 0.563 vs OMi 0.562 - rounding only, OMi kept) - same source as OMi (not a 2nd source); the non-forged Air-Way row of this size is NOT used; the generator MODEL text names the leg columns "Air-Way M5 / M10" - on this row they hold the OMi values above | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs) | hex A/F raised from Air-Way 0.56 to 0.5625 (JIC thread major; 2603HX rule)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-06-04 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-02 (batch 15, staged for review): this -FG part's own dimensions from OMi WebsitePartsInfo2026.xlsx Items row 1915 (= Brennan TFA p34 6500-06-04-FG, one source) - ASSUMED; catalog rounding-only prints: HEXB@HEX: catalog C HEX 0.563 vs OMi 0.562 - rounding only, OMi kept; open, NON-gating: Q-NEW-MS51531NUT (optional routes to VERIFIED only - TaskC_resort.md 3d "never gate building": Q-NEW-MS51531NUT = MS51531D tube-nut hex as a 2nd source for the swivel nut hex) | hex A/F raised from Air-Way 0.562 to 0.5625 (JIC thread major; 2603HX rule)</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>6500-06-06-FG</t>
+          <t>6500-06-04-FG</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6500-06-08-FG</t>
+          <t>6500-06-06-FG</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="C7" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="D7" t="n">
         <v>0.28125</v>
@@ -1860,76 +1860,76 @@
         <v>37</v>
       </c>
       <c r="L7" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="M7" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="N7" t="n">
-        <v>0.885</v>
+        <v>0.785</v>
       </c>
       <c r="O7" t="n">
-        <v>0.292</v>
+        <v>0.206</v>
       </c>
       <c r="P7" t="n">
-        <v>0.827</v>
+        <v>0.735</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4108</v>
+        <v>0.3224</v>
       </c>
       <c r="R7" t="n">
-        <v>0.18</v>
+        <v>0.145</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4361</v>
+        <v>0.3428</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4499</v>
+        <v>0.3876</v>
       </c>
       <c r="U7" t="n">
-        <v>0.50807</v>
+        <v>0.39837</v>
       </c>
       <c r="V7" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="W7" t="n">
-        <v>0.34117</v>
+        <v>0.25118</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3283</v>
+        <v>0.2945</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3925</v>
+        <v>0.2925</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6723</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.34</v>
+        <v>0.246</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.42</v>
+        <v>0.37</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.2825</v>
+        <v>0.215</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.88</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.4499</v>
+        <v>0.3876</v>
       </c>
       <c r="AF7" t="n">
         <v>0.3</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AJ7" t="n">
         <v>0.5625</v>
@@ -1950,58 +1950,58 @@
         <v>0.05556</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.6823399999999999</v>
+        <v>0.50236</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.3567</v>
+        <v>0.3197</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.34117</v>
+        <v>0.25118</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.584</v>
+        <v>0.504</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.495</v>
+        <v>0.465</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.21651</v>
+        <v>0.16188</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.21651</v>
+        <v>0.16188</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.43301</v>
+        <v>0.32426</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>6500-06-08-FG</t>
+          <t>6500-06-06-FG</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 9/16-18 JIC x 3/4-16 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 9/16-18 JIC x 9/16-18 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>3/4-16 (female 37deg JIC swivel)</t>
+          <t>9/16-18 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2031,44 +2031,44 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs)</t>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs) | hex A/F raised from Air-Way 0.56 to 0.5625 (JIC thread major; 2603HX rule)</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>6500-06-08-FG</t>
+          <t>6500-06-06-FG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6500-08-10-FG</t>
+          <t>6500-06-08-FG</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="C8" t="n">
-        <v>0.44</v>
+        <v>0.375</v>
       </c>
       <c r="D8" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="E8" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2837</v>
+        <v>0.2515</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3295</v>
+        <v>0.2405</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0984</v>
+        <v>0.0898</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
@@ -2077,148 +2077,148 @@
         <v>37</v>
       </c>
       <c r="L8" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="M8" t="n">
-        <v>0.44</v>
+        <v>0.375</v>
       </c>
       <c r="N8" t="n">
-        <v>0.985</v>
+        <v>0.885</v>
       </c>
       <c r="O8" t="n">
-        <v>0.347</v>
+        <v>0.292</v>
       </c>
       <c r="P8" t="n">
-        <v>0.944</v>
+        <v>0.827</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4758</v>
+        <v>0.4108</v>
       </c>
       <c r="R8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4988</v>
+        <v>0.4361</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5265</v>
+        <v>0.4499</v>
       </c>
       <c r="U8" t="n">
-        <v>0.57735</v>
+        <v>0.50807</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="W8" t="n">
-        <v>0.39884</v>
+        <v>0.34117</v>
       </c>
       <c r="X8" t="n">
-        <v>0.404</v>
+        <v>0.3283</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4475</v>
+        <v>0.3925</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.7794</v>
+        <v>0.6723</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.394</v>
+        <v>0.34</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.3375</v>
+        <v>0.2825</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.5265</v>
+        <v>0.4499</v>
       </c>
       <c r="AF8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH8" t="n">
         <v>0.39</v>
       </c>
-      <c r="AG8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.48</v>
-      </c>
       <c r="AI8" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AJ8" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.03007</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.6823399999999999</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AV8" t="n">
         <v>0.75</v>
       </c>
-      <c r="AK8" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0.2837</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.03383</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0.01562</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0.7976799999999999</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0.4364</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0.07142999999999999</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0.39884</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0.4375</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0.88</v>
-      </c>
       <c r="AW8" t="n">
-        <v>0.673</v>
+        <v>0.584</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.635</v>
+        <v>0.495</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.44</v>
+        <v>0.375</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.44</v>
+        <v>0.375</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.25403</v>
+        <v>0.21601</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.25403</v>
+        <v>0.21601</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.50807</v>
+        <v>0.43251</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>6500-08-10-FG</t>
+          <t>6500-06-08-FG</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 3/4-16 JIC x 7/8-14 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 9/16-18 JIC x 3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>3/4-16 JIC</t>
+          <t>9/16-18 JIC</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>7/8-14 (female 37deg JIC swivel)</t>
+          <t>3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -2253,21 +2253,21 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>6500-08-10-FG</t>
+          <t>6500-06-08-FG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6500-08-12-FG</t>
+          <t>6500-08-10-FG</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="C9" t="n">
-        <v>0.531</v>
+        <v>0.44</v>
       </c>
       <c r="D9" t="n">
         <v>0.375</v>
@@ -2294,76 +2294,76 @@
         <v>37</v>
       </c>
       <c r="L9" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="M9" t="n">
-        <v>0.531</v>
+        <v>0.44</v>
       </c>
       <c r="N9" t="n">
-        <v>1.089</v>
+        <v>0.985</v>
       </c>
       <c r="O9" t="n">
-        <v>0.417</v>
+        <v>0.347</v>
       </c>
       <c r="P9" t="n">
-        <v>1.047</v>
+        <v>0.944</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5928</v>
+        <v>0.4758</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6237</v>
+        <v>0.4988</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5998</v>
+        <v>0.5265</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.57735</v>
       </c>
       <c r="V9" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="W9" t="n">
-        <v>0.48614</v>
+        <v>0.39884</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4472</v>
+        <v>0.404</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.549</v>
+        <v>0.4475</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.8623</v>
+        <v>0.7794</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.481</v>
+        <v>0.394</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.4225</v>
+        <v>0.3375</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.5998</v>
+        <v>0.5265</v>
       </c>
       <c r="AF9" t="n">
         <v>0.39</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AJ9" t="n">
         <v>0.75</v>
@@ -2384,58 +2384,58 @@
         <v>0.0625</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.97228</v>
+        <v>0.7976799999999999</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.4851</v>
+        <v>0.4364</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.48614</v>
+        <v>0.39884</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.062</v>
+        <v>0.88</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.763</v>
+        <v>0.673</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.062</v>
+        <v>0.88</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.661</v>
+        <v>0.635</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.531</v>
+        <v>0.44</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.531</v>
+        <v>0.44</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.30657</v>
+        <v>0.25353</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.30657</v>
+        <v>0.25353</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.61315</v>
+        <v>0.50757</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>6500-08-12-FG</t>
+          <t>6500-08-10-FG</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 3/4-16 JIC x 1 1/16-12 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 3/4-16 JIC x 7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female 37deg JIC swivel)</t>
+          <t>7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R1921 Hex Flat = 1.062 (table had 1.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
@@ -2470,36 +2470,36 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>6500-08-12-FG</t>
+          <t>6500-08-10-FG</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6500-10-08-FG</t>
+          <t>6500-08-12-FG</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="C10" t="n">
-        <v>0.44</v>
+        <v>0.531</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="E10" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3553</v>
+        <v>0.2837</v>
       </c>
       <c r="G10" t="n">
-        <v>0.386</v>
+        <v>0.3295</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1114</v>
+        <v>0.0984</v>
       </c>
       <c r="I10" t="n">
         <v>0.1546</v>
@@ -2511,148 +2511,148 @@
         <v>37</v>
       </c>
       <c r="L10" t="n">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0.44</v>
+        <v>0.531</v>
       </c>
       <c r="N10" t="n">
-        <v>0.885</v>
+        <v>1.089</v>
       </c>
       <c r="O10" t="n">
-        <v>0.292</v>
+        <v>0.417</v>
       </c>
       <c r="P10" t="n">
-        <v>0.827</v>
+        <v>1.047</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4108</v>
+        <v>0.5928</v>
       </c>
       <c r="R10" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4361</v>
+        <v>0.6237</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4499</v>
+        <v>0.5998</v>
       </c>
       <c r="U10" t="n">
-        <v>0.50807</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0.375</v>
+        <v>0.53125</v>
       </c>
       <c r="W10" t="n">
-        <v>0.34117</v>
+        <v>0.48614</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3283</v>
+        <v>0.4472</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3925</v>
+        <v>0.549</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.6723</v>
+        <v>0.8623</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.34</v>
+        <v>0.481</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.42</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.2825</v>
+        <v>0.4225</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.88</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.4499</v>
+        <v>0.5998</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.48</v>
+        <v>0.39</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.39</v>
+        <v>0.61</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.3553</v>
+        <v>0.2837</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.03866</v>
+        <v>0.03383</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.01786</v>
+        <v>0.01562</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.6823399999999999</v>
+        <v>0.97228</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.3567</v>
+        <v>0.4851</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.0625</v>
+        <v>0.08333</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.34117</v>
+        <v>0.48614</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.375</v>
+        <v>0.53125</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.88</v>
+        <v>1.062</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.763</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.88</v>
+        <v>1.062</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.625</v>
+        <v>0.661</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.44</v>
+        <v>0.531</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.44</v>
+        <v>0.531</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.25403</v>
+        <v>0.30607</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.25403</v>
+        <v>0.30607</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.50807</v>
+        <v>0.61265</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>6500-10-08-FG</t>
+          <t>6500-08-12-FG</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 7/8-14 JIC x 3/4-16 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 3/4-16 JIC x 1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -2662,12 +2662,12 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>7/8-14 JIC</t>
+          <t>3/4-16 JIC</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>3/4-16 (female 37deg JIC swivel)</t>
+          <t>1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R1921 Hex Flat = 1.062 (table had 1.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
@@ -2687,14 +2687,14 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>6500-10-08-FG</t>
+          <t>6500-08-12-FG</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6500-10-10-FG</t>
+          <t>6500-10-08-FG</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2728,64 +2728,64 @@
         <v>37</v>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="M11" t="n">
         <v>0.44</v>
       </c>
       <c r="N11" t="n">
-        <v>0.985</v>
+        <v>0.885</v>
       </c>
       <c r="O11" t="n">
-        <v>0.347</v>
+        <v>0.292</v>
       </c>
       <c r="P11" t="n">
-        <v>0.944</v>
+        <v>0.827</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4758</v>
+        <v>0.4108</v>
       </c>
       <c r="R11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4988</v>
+        <v>0.4361</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5265</v>
+        <v>0.4499</v>
       </c>
       <c r="U11" t="n">
-        <v>0.57735</v>
+        <v>0.50807</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="W11" t="n">
-        <v>0.39884</v>
+        <v>0.34117</v>
       </c>
       <c r="X11" t="n">
-        <v>0.404</v>
+        <v>0.3283</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4475</v>
+        <v>0.3925</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.7794</v>
+        <v>0.6723</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.394</v>
+        <v>0.34</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.3375</v>
+        <v>0.2825</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.5265</v>
+        <v>0.4499</v>
       </c>
       <c r="AF11" t="n">
         <v>0.48</v>
@@ -2794,10 +2794,10 @@
         <v>1.45</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.48</v>
+        <v>0.39</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AJ11" t="n">
         <v>0.875</v>
@@ -2818,22 +2818,22 @@
         <v>0.07142999999999999</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.7976799999999999</v>
+        <v>0.6823399999999999</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.4364</v>
+        <v>0.3567</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.39884</v>
+        <v>0.34117</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AV11" t="n">
         <v>0.88</v>
@@ -2845,7 +2845,7 @@
         <v>0.88</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.635</v>
+        <v>0.625</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.44</v>
@@ -2854,22 +2854,22 @@
         <v>0.44</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>6500-10-10-FG</t>
+          <t>6500-10-08-FG</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 7/8-14 JIC x 7/8-14 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 7/8-14 JIC x 3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>7/8-14 (female 37deg JIC swivel)</t>
+          <t>3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -2899,26 +2899,26 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs)</t>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs)</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>6500-10-10-FG</t>
+          <t>6500-10-08-FG</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6500-10-12-FG</t>
+          <t>6500-10-10-FG</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="C12" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="D12" t="n">
         <v>0.4375</v>
@@ -2945,76 +2945,76 @@
         <v>37</v>
       </c>
       <c r="L12" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="M12" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="N12" t="n">
-        <v>1.089</v>
+        <v>0.985</v>
       </c>
       <c r="O12" t="n">
-        <v>0.417</v>
+        <v>0.347</v>
       </c>
       <c r="P12" t="n">
-        <v>1.047</v>
+        <v>0.944</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.5928</v>
+        <v>0.4758</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6237</v>
+        <v>0.4988</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5998</v>
+        <v>0.5265</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.57735</v>
       </c>
       <c r="V12" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="W12" t="n">
-        <v>0.48614</v>
+        <v>0.39884</v>
       </c>
       <c r="X12" t="n">
-        <v>0.4472</v>
+        <v>0.404</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.549</v>
+        <v>0.4475</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.8623</v>
+        <v>0.7794</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.481</v>
+        <v>0.394</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.4225</v>
+        <v>0.3375</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.5998</v>
+        <v>0.5265</v>
       </c>
       <c r="AF12" t="n">
         <v>0.48</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AJ12" t="n">
         <v>0.875</v>
@@ -3035,58 +3035,58 @@
         <v>0.07142999999999999</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.97228</v>
+        <v>0.7976799999999999</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.4851</v>
+        <v>0.4364</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.48614</v>
+        <v>0.39884</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.782</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.661</v>
+        <v>0.635</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.306</v>
+        <v>0.25353</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.306</v>
+        <v>0.25353</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.61199</v>
+        <v>0.50757</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>6500-10-12-FG</t>
+          <t>6500-10-10-FG</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 7/8-14 JIC x 1 1/16-12 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 7/8-14 JIC x 7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female 37deg JIC swivel)</t>
+          <t>7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -3116,44 +3116,44 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs)</t>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs)</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>6500-10-12-FG</t>
+          <t>6500-10-10-FG</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6500-16-16-FG</t>
+          <t>6500-10-12-FG</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="C13" t="n">
-        <v>0.65625</v>
+        <v>0.53</v>
       </c>
       <c r="D13" t="n">
-        <v>0.65625</v>
+        <v>0.4375</v>
       </c>
       <c r="E13" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4365</v>
+        <v>0.3553</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5965</v>
+        <v>0.386</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1292</v>
+        <v>0.1114</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1858</v>
+        <v>0.1546</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
@@ -3162,148 +3162,148 @@
         <v>37</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>0.65625</v>
+        <v>0.53</v>
       </c>
       <c r="N13" t="n">
-        <v>1.175</v>
+        <v>1.089</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5485</v>
+        <v>0.417</v>
       </c>
       <c r="P13" t="n">
-        <v>1.139</v>
+        <v>1.047</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.727</v>
+        <v>0.5928</v>
       </c>
       <c r="R13" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="S13" t="n">
-        <v>0.749</v>
+        <v>0.6237</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6564</v>
+        <v>0.5998</v>
       </c>
       <c r="U13" t="n">
-        <v>0.86603</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="W13" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="X13" t="n">
-        <v>0.4873</v>
+        <v>0.4472</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.665</v>
+        <v>0.549</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.9544</v>
+        <v>0.8623</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.604</v>
+        <v>0.481</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.5475</v>
+        <v>0.4225</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.6564</v>
+        <v>0.5998</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.84</v>
+        <v>0.48</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AI13" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3125</v>
+        <v>0.875</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.4365</v>
+        <v>0.3553</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.22228</v>
+        <v>0.97228</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.5252</v>
+        <v>0.4851</v>
       </c>
       <c r="AR13" t="n">
         <v>0.08333</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="AU13" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.3125</v>
+        <v>1.06</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.899</v>
+        <v>0.782</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.3125</v>
+        <v>1.06</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.825</v>
+        <v>0.661</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.65625</v>
+        <v>0.53</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.65625</v>
+        <v>0.53</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.37889</v>
+        <v>0.3055</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.37889</v>
+        <v>0.3055</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.7577700000000001</v>
+        <v>0.61149</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>6500-16-16-FG</t>
+          <t>6500-10-12-FG</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 1 5/16-12 JIC x 1 5/16-12 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 7/8-14 JIC x 1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>1 5/16-12 JIC</t>
+          <t>7/8-14 JIC</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female 37deg JIC swivel)</t>
+          <t>1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -3333,44 +3333,44 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>legs differ from MS51521: AW M=1.81/M5=2.0 vs MS 1.8/2.0; RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule)</t>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs)</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>6500-16-16-FG</t>
+          <t>6500-10-12-FG</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6500-20-20-FG</t>
+          <t>6500-12-08-FG</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.06</v>
+        <v>1.66</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8125</v>
+        <v>0.53125</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8125</v>
+        <v>0.53125</v>
       </c>
       <c r="E14" t="n">
         <v>0.125</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4316</v>
+        <v>0.3895</v>
       </c>
       <c r="G14" t="n">
-        <v>0.753</v>
+        <v>0.4715</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1288</v>
+        <v>0.1299</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2382</v>
+        <v>0.1851</v>
       </c>
       <c r="J14" t="n">
         <v>60</v>
@@ -3379,85 +3379,85 @@
         <v>37</v>
       </c>
       <c r="L14" t="n">
-        <v>2.31</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8125</v>
+        <v>0.53125</v>
       </c>
       <c r="N14" t="n">
-        <v>1.26</v>
+        <v>0.885</v>
       </c>
       <c r="O14" t="n">
-        <v>0.68</v>
+        <v>0.292</v>
       </c>
       <c r="P14" t="n">
-        <v>1.145</v>
+        <v>0.827</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.949</v>
+        <v>0.4108</v>
       </c>
       <c r="R14" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9889</v>
+        <v>0.4361</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5375</v>
+        <v>0.4499</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1547</v>
+        <v>0.50518</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8125</v>
+        <v>0.375</v>
       </c>
       <c r="W14" t="n">
-        <v>0.76739</v>
+        <v>0.34117</v>
       </c>
       <c r="X14" t="n">
-        <v>0.4345</v>
+        <v>0.3283</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.88</v>
+        <v>0.3925</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.9556</v>
+        <v>0.6723</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.766</v>
+        <v>0.34</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.62</v>
+        <v>0.42</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.7025</v>
+        <v>0.2825</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>0.875</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.5375</v>
+        <v>0.4499</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.08</v>
+        <v>0.609</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.06</v>
+        <v>1.66</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.08</v>
+        <v>0.391</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.31</v>
+        <v>1.55</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.625</v>
+        <v>1.0625</v>
       </c>
       <c r="AK14" t="n">
         <v>0.08333</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.4316</v>
+        <v>0.3895</v>
       </c>
       <c r="AM14" t="n">
         <v>0.04511</v>
@@ -3469,58 +3469,58 @@
         <v>0.08333</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.53478</v>
+        <v>0.6823399999999999</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.4724</v>
+        <v>0.3567</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.76739</v>
+        <v>0.34117</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.8125</v>
+        <v>0.375</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.31</v>
+        <v>1.55</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.625</v>
+        <v>1.0625</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.102</v>
+        <v>0.796</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.625</v>
+        <v>1.0625</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.05</v>
+        <v>0.665</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.8125</v>
+        <v>0.53125</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.8125</v>
+        <v>0.53125</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.4691</v>
+        <v>0.30622</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.4691</v>
+        <v>0.30622</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.93819</v>
+        <v>0.61293</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>6500-20-20-FG</t>
+          <t>6500-12-08-FG</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 1 5/8-12 JIC x 1 5/8-12 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 1 1/16-12 JIC x 3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>1 5/8-12 JIC</t>
+          <t>1 1/16-12 JIC</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>1 5/8-12 (female 37deg JIC swivel)</t>
+          <t>3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -3545,49 +3545,49 @@
       </c>
       <c r="BK14" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-12-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied; 2026-10-09 (left out of batch 15, staged): LEG_M@DRIVE: OMi Items row 1925 L 1 Size = 1.66; LEG_M5@DRIVE: OMi Items row 1925 M 2 Size = 1.55; LEG_M10@DRIVE: OMi Items row 1925 M 1 Size = 1.13; HEXB@HEX: OMi Items row 1925 Nut Hex 1 = 0.875; Y@REF: OMi Items row 1925 Hex Flat = 1.062; D1@BORE: OMi Items row 1925 Side 1 ID = 0.609; D2@BORE: OMi Items row 1925 Side 2 ID = 0.391; THDMAJ_A@DRIVE: 1 1/16-12 -&gt; 1.0625 (end library); THDMAJ_B@DRIVE: 3/4-16 -&gt; 0.75 (end library) [user 2026-09-25: OMi dims &gt; Air-Way; user 2026-10-08: no size from Brennan alone -&gt; OMi stands, ASSUMED]; pairing: OMi L 1 = male JIC leg (catalog M), M 2 = swivel-nut face (M6), M 1 = swivel nose / seat (M4), Hex Flat = body hex, Nut Hex 1 = swivel nut hex, Side 1 / 2 ID = bores of ends 1 / 2 (batch-15 pairing, Brennan TFA p34 letters) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs) | hex A/F raised from Air-Way 1.62 to 1.6250 (JIC thread major; 2603HX rule); leg 2: Air-Way nut-face-to-seat 0.620 vs Brennan 0.640</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-12-08 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-09 (staged): this part's own sizes from OMi WebsitePartsInfo2026 Items row 1925 - ASSUMED (one source). It was held in batch 15 because the Brennan TFA catalog prints other values for it; under the 2026-10-08 ruling the catalog (= OMi's source) is evidence only and OMi stands. Catalog print for the record: TFA-p034-t01: TUBE O.D. 3/4, B1 SAE 37Deg 1-1/16-12, B2 SAE 37Deg 3/4-16, B1 DRILL 0.609, B2 DRILL 0.391, M LGTH 1.660, M4 LGTH 1.120, M6 LGTH 1.550, C HEX 0.875, Y FLATS 1.062 | hex A/F raised from Air-Way 1.062 to 1.0625 (JIC thread major; 2603HX rule)</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>6500-20-20-FG</t>
+          <t>6500-12-08-FG</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6500-24-24-FG</t>
+          <t>6500-12-16-FG</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.33</v>
+        <v>1.76</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.656</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9375</v>
+        <v>0.53125</v>
       </c>
       <c r="E15" t="n">
         <v>0.125</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5454</v>
+        <v>0.3895</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.4715</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1298</v>
+        <v>0.1299</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2482</v>
+        <v>0.1851</v>
       </c>
       <c r="J15" t="n">
         <v>60</v>
@@ -3596,85 +3596,85 @@
         <v>37</v>
       </c>
       <c r="L15" t="n">
-        <v>2.59</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.656</v>
       </c>
       <c r="N15" t="n">
-        <v>1.41</v>
+        <v>1.175</v>
       </c>
       <c r="O15" t="n">
-        <v>0.776</v>
+        <v>0.5485</v>
       </c>
       <c r="P15" t="n">
-        <v>1.32</v>
+        <v>1.139</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.0504</v>
+        <v>0.727</v>
       </c>
       <c r="R15" t="n">
         <v>0.23</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1134</v>
+        <v>0.749</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7063</v>
+        <v>0.6564</v>
       </c>
       <c r="U15" t="n">
-        <v>1.29904</v>
+        <v>0.86603</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9375</v>
+        <v>0.65625</v>
       </c>
       <c r="W15" t="n">
-        <v>0.89239</v>
+        <v>0.61114</v>
       </c>
       <c r="X15" t="n">
-        <v>0.5295</v>
+        <v>0.4873</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.01</v>
+        <v>0.665</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.065</v>
+        <v>0.9544</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.8885</v>
+        <v>0.604</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.73</v>
+        <v>0.59</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.5475</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.7063</v>
+        <v>0.6564</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.31</v>
+        <v>0.609</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.33</v>
+        <v>1.76</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.31</v>
+        <v>0.844</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.59</v>
+        <v>2</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.875</v>
+        <v>1.0625</v>
       </c>
       <c r="AK15" t="n">
         <v>0.08333</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.5454</v>
+        <v>0.3895</v>
       </c>
       <c r="AM15" t="n">
         <v>0.04511</v>
@@ -3686,58 +3686,58 @@
         <v>0.08333</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.78478</v>
+        <v>1.22228</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.5674</v>
+        <v>0.5252</v>
       </c>
       <c r="AR15" t="n">
         <v>0.08333</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.89239</v>
+        <v>0.61114</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.9375</v>
+        <v>0.65625</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.59</v>
+        <v>2</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.88</v>
+        <v>1.312</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.247</v>
+        <v>0.896</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.88</v>
+        <v>1.312</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.18</v>
+        <v>0.825</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.656</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.656</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.54271</v>
+        <v>0.37824</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.54271</v>
+        <v>0.37824</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.08542</v>
+        <v>0.75698</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>6500-24-24-FG</t>
+          <t>6500-12-16-FG</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 1 7/8-12 JIC x 1 7/8-12 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 1 1/16-12 JIC x 1 5/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>1 7/8-12 JIC</t>
+          <t>1 1/16-12 JIC</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>1 7/8-12 (female 37deg JIC swivel)</t>
+          <t>1 5/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -3762,49 +3762,49 @@
       </c>
       <c r="BK15" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-12-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied; 2026-10-09 (left out of batch 15, staged): LEG_M@DRIVE: OMi Items row 1927 L 1 Size = 1.76; LEG_M5@DRIVE: OMi Items row 1927 M 2 Size = 2.00; LEG_M10@DRIVE: OMi Items row 1927 M 1 Size = 1.41; HEXB@HEX: OMi Items row 1927 Nut Hex 1 = 1.500; Y@REF: OMi Items row 1927 Hex Flat = 1.312; D1@BORE: OMi Items row 1927 Side 1 ID = 0.609; D2@BORE: OMi Items row 1927 Side 2 ID = 0.844; THDMAJ_A@DRIVE: 1 1/16-12 -&gt; 1.0625 (end library); THDMAJ_B@DRIVE: 1 5/16-12 -&gt; 1.3125 (end library) [user 2026-09-25: OMi dims &gt; Air-Way; user 2026-10-08: no size from Brennan alone -&gt; OMi stands, ASSUMED]; pairing: OMi L 1 = male JIC leg (catalog M), M 2 = swivel-nut face (M6), M 1 = swivel nose / seat (M4), Hex Flat = body hex, Nut Hex 1 = swivel nut hex, Side 1 / 2 ID = bores of ends 1 / 2 (batch-15 pairing, Brennan TFA p34 letters) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-12-16 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-09 (staged): this part's own sizes from OMi WebsitePartsInfo2026 Items row 1927 - ASSUMED (one source). It was held in batch 15 because the Brennan TFA catalog prints other values for it; under the 2026-10-08 ruling the catalog (= OMi's source) is evidence only and OMi stands. Catalog print for the record: TFA-p034-t01: TUBE O.D. 3/4, B1 SAE 37Deg 1-1/16-12, B2 SAE 37Deg 1-5/16-12, B1 DRILL 0.609, B2 DRILL 0.844, M LGTH 1.81, M4 LGTH 1.40, M6 LGTH 2.00, C HEX 1.500, Y FLATS 1.312</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>6500-24-24-FG</t>
+          <t>6500-12-16-FG</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6500-32-32-FG</t>
+          <t>6500-16-12-FG</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.06</v>
+        <v>1.81</v>
       </c>
       <c r="C16" t="n">
-        <v>1.25</v>
+        <v>0.65625</v>
       </c>
       <c r="D16" t="n">
-        <v>1.25</v>
+        <v>0.65625</v>
       </c>
       <c r="E16" t="n">
         <v>0.125</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7124</v>
+        <v>0.4365</v>
       </c>
       <c r="G16" t="n">
-        <v>1.19</v>
+        <v>0.5965</v>
       </c>
       <c r="H16" t="n">
         <v>0.1292</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3318</v>
+        <v>0.1858</v>
       </c>
       <c r="J16" t="n">
         <v>60</v>
@@ -3813,85 +3813,85 @@
         <v>37</v>
       </c>
       <c r="L16" t="n">
-        <v>3.38</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.5928</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.6237</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.7216900000000001</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.4472</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.8623</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.4225</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.25</v>
       </c>
-      <c r="N16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.0785</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.3936</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.4242</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.862</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.66277</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.20489</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.702</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.325</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.4202</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.198</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.1175</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AE16" t="n">
-        <v>0.862</v>
+        <v>0.5998</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.78</v>
+        <v>0.844</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.06</v>
+        <v>1.81</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.78</v>
+        <v>0.609</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.38</v>
+        <v>1.95</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.5</v>
+        <v>1.3125</v>
       </c>
       <c r="AK16" t="n">
         <v>0.08333</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.7124</v>
+        <v>0.4365</v>
       </c>
       <c r="AM16" t="n">
         <v>0.04511</v>
@@ -3903,93 +3903,2046 @@
         <v>0.08333</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.40978</v>
+        <v>0.97228</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.7399</v>
+        <v>0.4851</v>
       </c>
       <c r="AR16" t="n">
         <v>0.08333</v>
       </c>
       <c r="AS16" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0.75727</v>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>6500-16-12-FG</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>90 deg Female Swivel Elbow, 1 5/16-12 JIC x 1 1/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>6500</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>1 5/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-16-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied; 2026-10-09 (left out of batch 15, staged): LEG_M@DRIVE: OMi Items row 1928 L 1 Size = 1.81; LEG_M5@DRIVE: OMi Items row 1928 M 2 Size = 1.95; LEG_M10@DRIVE: OMi Items row 1928 M 1 Size = 1.39; HEXB@HEX: OMi Items row 1928 Nut Hex 1 = 1.250; Y@REF: OMi Items row 1928 Hex Flat = 1.312; D1@BORE: OMi Items row 1928 Side 1 ID = 0.844; D2@BORE: OMi Items row 1928 Side 2 ID = 0.609; THDMAJ_A@DRIVE: 1 5/16-12 -&gt; 1.3125 (end library); THDMAJ_B@DRIVE: 1 1/16-12 -&gt; 1.0625 (end library) [user 2026-09-25: OMi dims &gt; Air-Way; user 2026-10-08: no size from Brennan alone -&gt; OMi stands, ASSUMED]; pairing: OMi L 1 = male JIC leg (catalog M), M 2 = swivel-nut face (M6), M 1 = swivel nose / seat (M4), Hex Flat = body hex, Nut Hex 1 = swivel nut hex, Side 1 / 2 ID = bores of ends 1 / 2 (batch-15 pairing, Brennan TFA p34 letters) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-16-12 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-09 (staged): this part's own sizes from OMi WebsitePartsInfo2026 Items row 1928 - ASSUMED (one source). It was held in batch 15 because the Brennan TFA catalog prints other values for it; under the 2026-10-08 ruling the catalog (= OMi's source) is evidence only and OMi stands. Catalog print for the record: TFA-p034-t01: TUBE O.D. 1, B1 SAE 37Deg 1-5/16-12, B2 SAE 37Deg 1-1/16-12, B1 DRILL 0.844, B2 DRILL 0.609, M LGTH 1.81, M4 LGTH 1.34, M6 LGTH 1.91, C HEX 1.250, Y FLATS 1.312 | hex A/F raised from Air-Way 1.312 to 1.3125 (JIC thread major; 2603HX rule)</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>6500-16-12-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>6500-16-16-FG</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="J17" t="n">
+        <v>60</v>
+      </c>
+      <c r="K17" t="n">
+        <v>37</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.5485</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.6564</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.86603</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.61114</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.4873</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.9544</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.5475</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.6564</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.22228</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0.5252</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0.61114</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0.75727</v>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>6500-16-16-FG</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>90 deg Female Swivel Elbow, 1 5/16-12 JIC x 1 5/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>6500</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>1 5/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>legs differ from MS51521: AW M=1.81/M5=2.0 vs MS 1.8/2.0; RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule)</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>6500-16-16-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6500-20-20-FG</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="J18" t="n">
+        <v>60</v>
+      </c>
+      <c r="K18" t="n">
+        <v>37</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.9889</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.1547</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.4345</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.9556</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.53478</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.4724</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0.93769</v>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>6500-20-20-FG</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>90 deg Female Swivel Elbow, 1 5/8-12 JIC x 1 5/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>6500</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>1 5/8-12 JIC</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs) | hex A/F raised from Air-Way 1.62 to 1.6250 (JIC thread major; 2603HX rule); leg 2: Air-Way nut-face-to-seat 0.620 vs Brennan 0.640</t>
+        </is>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>6500-20-20-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6500-24-24-FG</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.8774999999999999</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="J19" t="n">
+        <v>60</v>
+      </c>
+      <c r="K19" t="n">
+        <v>37</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.0504</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.1134</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.7063</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.29904</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.89239</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.5295</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.8885</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.7063</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.78478</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.5674</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0.89239</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.247</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0.54221</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0.54221</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1.08492</v>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>6500-24-24-FG</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>90 deg Female Swivel Elbow, 1 7/8-12 JIC x 1 7/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>6500</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>1 7/8-12 JIC</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs)</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>6500-24-24-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>6500-32-32-FG</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="J20" t="n">
+        <v>60</v>
+      </c>
+      <c r="K20" t="n">
+        <v>37</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.0785</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.3936</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.4242</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.66277</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W20" t="n">
         <v>1.20489</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="X20" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.4202</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.198</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.1175</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>2.40978</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.7399</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.20489</v>
+      </c>
+      <c r="AT20" t="n">
         <v>1.25</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="AU20" t="n">
         <v>3.38</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="AV20" t="n">
         <v>2.5</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="AW20" t="n">
         <v>1.727</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="AX20" t="n">
         <v>2.5</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="AY20" t="n">
         <v>1.71</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="AZ20" t="n">
         <v>1.25</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BA20" t="n">
         <v>1.25</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BB20" t="n">
+        <v>0.72119</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0.72119</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.44288</v>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>6500-32-32-FG</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>90 deg Female Swivel Elbow, 2 1/2-12 JIC x 2 1/2-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>6500</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2 1/2-12 JIC</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>2 1/2-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs)</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>6500-32-32-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6500-L-04-04-FG</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.0795</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="J21" t="n">
+        <v>60</v>
+      </c>
+      <c r="K21" t="n">
+        <v>37</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.1465</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.2574</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.19169</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.5243</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.1845</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0.02706</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0.2867</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0.19169</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.475</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0.12594</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0.12594</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0.25238</v>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>6500-L-04-04-FG</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>90 deg Female Swivel Elbow, 7/16-20 JIC x 7/16-20 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>6500</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>7/16-20 JIC</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>7/16-20 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>OMi WebsitePartsInfo2026.xlsx Items row 1936 (OMi first, user decision 2026-09-25): M = L 1, M9 = M 2 (crossing to the swivel-nut face), M12 = M 1 (crossing to the nose tip), Y = Hex Flat, CHEX = Nut Hex 1, D1 / D2 = Side 1 / Side 2 ID - column meaning from the Brennan TFA catalog p34 drawing letters (M / M6 / M4 / Y FLATS / C HEX / B1 / B2 DRILL, OMi = catalog 5/5); OMi and Brennan are ONE source -&gt; ASSUMED; male JIC end VERIFIED (MS33656J) | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-L-04-04 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): the forged swivel hex arm runs on to the swivel end of the same size (BRENNAN_6500-L-08-08-FG; its length through the swivel end-library constant SW2_BODYS); the sizes of the part are OMi's | FOLD: 6500-L fold: the extra length is the forged swivel hex arm, the swivel end is the 6500 one of the same size (Brennan 6500-L-08-08-FG STEP, tools/measure/swiv.py + elbow90.py: swivel end = SWIV_MEAS[8], arm 0..1.925 continuous; measured at -08 only, ASSUMED for the other sizes) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(OMi Hex Flat (Y), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = OMi Nut Hex 1 (CHEX) over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at OMi M 1 Size (M12), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = OMi M 2 Size (M9, crossing to the nut face), nose tip at OMi M 1 Size (M12, crossing to the nose tip); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-L-04-04 dims are NOT assumed; confirm before modelling | FOLDS 2026-10-02: filled from OMi Items row 1936; Brennan TFA catalog p34 (same source) differs only in the last printed digit (the catalog cuts OMi M 1 to 2 decimals, QA_Log #158; 9/16 = 0.5625 printed 0.562 / 0.563): M12 OMi 1.816 vs catalog 1.81; CHEX OMi 0.563 vs catalog 0.562 | 6500-L row folded into the 6500 master: Brennan 6500-L-08-08-FG STEP (pilot) = 6500-08-08-FG with the forged swivel hex arm 1.430 longer (Q-NEW-FOLD-6500L, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>6500-L-04-04-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6500-L-06-06-FG</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.2405</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.1082</v>
+      </c>
+      <c r="J22" t="n">
+        <v>60</v>
+      </c>
+      <c r="K22" t="n">
+        <v>37</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.39722</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.25118</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.5953000000000001</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0.03007</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0.50236</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0.25118</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.755</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0.16188</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0.16188</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>6500-L-06-06-FG</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>90 deg Female Swivel Elbow, 9/16-18 JIC x 9/16-18 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>6500</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>9/16-18 JIC</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>9/16-18 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>OMi WebsitePartsInfo2026.xlsx Items row 1937 (OMi first, user decision 2026-09-25): M = L 1, M9 = M 2 (crossing to the swivel-nut face), M12 = M 1 (crossing to the nose tip), Y = Hex Flat, CHEX = Nut Hex 1, D1 / D2 = Side 1 / Side 2 ID - column meaning from the Brennan TFA catalog p34 drawing letters (M / M6 / M4 / Y FLATS / C HEX / B1 / B2 DRILL, OMi = catalog 5/5); OMi and Brennan are ONE source -&gt; ASSUMED; male JIC end VERIFIED (MS33656J) | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-L-06-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): the forged swivel hex arm runs on to the swivel end of the same size (BRENNAN_6500-L-08-08-FG; its length through the swivel end-library constant SW2_BODYS); the sizes of the part are OMi's | FOLD: 6500-L fold: the extra length is the forged swivel hex arm, the swivel end is the 6500 one of the same size (Brennan 6500-L-08-08-FG STEP, tools/measure/swiv.py + elbow90.py: swivel end = SWIV_MEAS[8], arm 0..1.925 continuous; measured at -08 only, ASSUMED for the other sizes) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(OMi Hex Flat (Y), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = OMi Nut Hex 1 (CHEX) over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at OMi M 1 Size (M12), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = OMi M 2 Size (M9, crossing to the nut face), nose tip at OMi M 1 Size (M12, crossing to the nose tip); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-L-06-06 dims are NOT assumed; confirm before modelling | FOLDS 2026-10-02: filled from OMi Items row 1937; Brennan TFA catalog p34 (same source) differs only in the last printed digit (the catalog cuts OMi M 1 to 2 decimals, QA_Log #158; 9/16 = 0.5625 printed 0.562 / 0.563): M12 OMi 2.165 vs catalog 2.16 | 6500-L row folded into the 6500 master: Brennan 6500-L-08-08-FG STEP (pilot) = 6500-08-08-FG with the forged swivel hex arm 1.430 longer (Q-NEW-FOLD-6500L, 2026-10-02) | hex A/F raised from OMi Hex Flat 0.562 to 0.5625 (JIC thread major; 2603HX rule)</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>6500-L-06-06-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6500-L-08-08-FG</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="J23" t="n">
+        <v>60</v>
+      </c>
+      <c r="K23" t="n">
+        <v>37</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.4108</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.4361</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.50518</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.6723</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.2825</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.6823399999999999</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.925</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0.43251</v>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>6500-L-08-08-FG</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>90 deg Female Swivel Elbow, 3/4-16 JIC x 3/4-16 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>6500</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>3/4-16 JIC</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>3/4-16 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>OMi WebsitePartsInfo2026.xlsx Items row 1938 (OMi first, user decision 2026-09-25): M = L 1, M9 = M 2 (crossing to the swivel-nut face), M12 = M 1 (crossing to the nose tip), Y = Hex Flat, CHEX = Nut Hex 1, D1 / D2 = Side 1 / Side 2 ID - column meaning from the Brennan TFA catalog p34 drawing letters (M / M6 / M4 / Y FLATS / C HEX / B1 / B2 DRILL, OMi = catalog 5/5); OMi and Brennan are ONE source -&gt; ASSUMED; male JIC end VERIFIED (MS33656J) | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-L-08-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): the forged swivel hex arm runs on to the swivel end of the same size (BRENNAN_6500-L-08-08-FG; its length through the swivel end-library constant SW2_BODYS); the sizes of the part are OMi's | FOLD: 6500-L fold: the extra length is the forged swivel hex arm, the swivel end is the 6500 one of the same size (Brennan 6500-L-08-08-FG STEP, tools/measure/swiv.py + elbow90.py: swivel end = SWIV_MEAS[8], arm 0..1.925 continuous; measured at -08 only, ASSUMED for the other sizes) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(OMi Hex Flat (Y), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = OMi Nut Hex 1 (CHEX) over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at OMi M 1 Size (M12), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = OMi M 2 Size (M9, crossing to the nut face), nose tip at OMi M 1 Size (M12, crossing to the nose tip); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-L-08-08 dims are NOT assumed; confirm before modelling | FOLDS 2026-10-02: filled from OMi Items row 1938; Brennan TFA catalog p34 (same source) differs only in the last printed digit (the catalog cuts OMi M 1 to 2 decimals, QA_Log #158; 9/16 = 0.5625 printed 0.562 / 0.563): M12 OMi 2.388 vs catalog 2.38; Brennan 6500-L-08-08-FG STEP (pilot, elbow90.py + swiv.py): M 1.2501; M9 2.8101; M12 2.3801; Y 0.75; CHEX 0.875; D1 0.391; D2 0.391 - equal to OMi except the nose tip M12 (STEP 2.3801 = nut face 2.8101 - 0.43; OMi 2.388, +0.008, the same offset as OMi / Air-Way 0.96 vs the 6500-08-08-FG STEP 0.95) - built to OMi | 6500-L row folded into the 6500 master: Brennan 6500-L-08-08-FG STEP (pilot) = 6500-08-08-FG with the forged swivel hex arm 1.430 longer (Q-NEW-FOLD-6500L, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>6500-L-08-08-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6500-L-12-12-FG</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.4715</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="J24" t="n">
+        <v>60</v>
+      </c>
+      <c r="K24" t="n">
+        <v>37</v>
+      </c>
+      <c r="L24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.5928</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.6237</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="U24" t="n">
         <v>0.7216900000000001</v>
       </c>
-      <c r="BC16" t="n">
-        <v>0.7216900000000001</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>1.44338</v>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>6500-32-32-FG</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>90 deg Female Swivel Elbow, 2 1/2-12 JIC x 2 1/2-12 (female 37deg JIC swivel)</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
+      <c r="V24" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.4472</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.8623</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.4225</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0.97228</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0.4851</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>3.211</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0.61293</v>
+      </c>
+      <c r="BE24" t="inlineStr">
+        <is>
+          <t>6500-L-12-12-FG</t>
+        </is>
+      </c>
+      <c r="BF24" t="inlineStr">
+        <is>
+          <t>90 deg Female Swivel Elbow, 1 1/16-12 JIC x 1 1/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BG24" t="inlineStr">
         <is>
           <t>6500</t>
         </is>
       </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>2 1/2-12 JIC</t>
-        </is>
-      </c>
-      <c r="BI16" t="inlineStr">
-        <is>
-          <t>2 1/2-12 (female 37deg JIC swivel)</t>
-        </is>
-      </c>
-      <c r="BJ16" t="inlineStr">
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>1 1/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BJ24" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="BK16" t="inlineStr">
-        <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
-        </is>
-      </c>
-      <c r="BL16" t="inlineStr">
-        <is>
-          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs)</t>
-        </is>
-      </c>
-      <c r="BM16" t="inlineStr">
-        <is>
-          <t>6500-32-32-FG</t>
+      <c r="BK24" t="inlineStr">
+        <is>
+          <t>OMi WebsitePartsInfo2026.xlsx Items row 1939 (OMi first, user decision 2026-09-25): M = L 1, M9 = M 2 (crossing to the swivel-nut face), M12 = M 1 (crossing to the nose tip), Y = Hex Flat, CHEX = Nut Hex 1, D1 / D2 = Side 1 / Side 2 ID - column meaning from the Brennan TFA catalog p34 drawing letters (M / M6 / M4 / Y FLATS / C HEX / B1 / B2 DRILL, OMi = catalog 5/5); OMi and Brennan are ONE source -&gt; ASSUMED; male JIC end VERIFIED (MS33656J) | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-L-12-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): the forged swivel hex arm runs on to the swivel end of the same size (BRENNAN_6500-L-08-08-FG; its length through the swivel end-library constant SW2_BODYS); the sizes of the part are OMi's | FOLD: 6500-L fold: the extra length is the forged swivel hex arm, the swivel end is the 6500 one of the same size (Brennan 6500-L-08-08-FG STEP, tools/measure/swiv.py + elbow90.py: swivel end = SWIV_MEAS[8], arm 0..1.925 continuous; measured at -08 only, ASSUMED for the other sizes) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(OMi Hex Flat (Y), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = OMi Nut Hex 1 (CHEX) over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at OMi M 1 Size (M12), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = OMi M 2 Size (M9, crossing to the nut face), nose tip at OMi M 1 Size (M12, crossing to the nose tip); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BL24" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-L-12-12 dims are NOT assumed; confirm before modelling | FOLDS 2026-10-02: filled from OMi Items row 1939; Brennan TFA catalog p34 (same source) differs only in the last printed digit (the catalog cuts OMi M 1 to 2 decimals, QA_Log #158; 9/16 = 0.5625 printed 0.562 / 0.563): M12 OMi 3.738 vs catalog 3.73 | 6500-L row folded into the 6500 master: Brennan 6500-L-08-08-FG STEP (pilot) = 6500-08-08-FG with the forged swivel hex arm 1.430 longer (Q-NEW-FOLD-6500L, 2026-10-02) | hex A/F raised from OMi Hex Flat 1.062 to 1.0625 (JIC thread major; 2603HX rule)</t>
+        </is>
+      </c>
+      <c r="BM24" t="inlineStr">
+        <is>
+          <t>6500-L-12-12-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6500-L-16-16-FG</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="J25" t="n">
+        <v>60</v>
+      </c>
+      <c r="K25" t="n">
+        <v>37</v>
+      </c>
+      <c r="L25" t="n">
+        <v>5</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.5485</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.6564</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.86603</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.61114</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.4873</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.9544</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.5475</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0.6564</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.22228</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0.5252</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0.61114</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0.75727</v>
+      </c>
+      <c r="BE25" t="inlineStr">
+        <is>
+          <t>6500-L-16-16-FG</t>
+        </is>
+      </c>
+      <c r="BF25" t="inlineStr">
+        <is>
+          <t>90 deg Female Swivel Elbow, 1 5/16-12 JIC x 1 5/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BG25" t="inlineStr">
+        <is>
+          <t>6500</t>
+        </is>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>1 5/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BJ25" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BK25" t="inlineStr">
+        <is>
+          <t>OMi WebsitePartsInfo2026.xlsx Items row 1940 (OMi first, user decision 2026-09-25): M = L 1, M9 = M 2 (crossing to the swivel-nut face), M12 = M 1 (crossing to the nose tip), Y = Hex Flat, CHEX = Nut Hex 1, D1 / D2 = Side 1 / Side 2 ID - column meaning from the Brennan TFA catalog p34 drawing letters (M / M6 / M4 / Y FLATS / C HEX / B1 / B2 DRILL, OMi = catalog 5/5); OMi and Brennan are ONE source -&gt; ASSUMED; male JIC end VERIFIED (MS33656J) | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-L-16-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): the forged swivel hex arm runs on to the swivel end of the same size (BRENNAN_6500-L-08-08-FG; its length through the swivel end-library constant SW2_BODYS); the sizes of the part are OMi's | FOLD: 6500-L fold: the extra length is the forged swivel hex arm, the swivel end is the 6500 one of the same size (Brennan 6500-L-08-08-FG STEP, tools/measure/swiv.py + elbow90.py: swivel end = SWIV_MEAS[8], arm 0..1.925 continuous; measured at -08 only, ASSUMED for the other sizes) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(OMi Hex Flat (Y), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = OMi Nut Hex 1 (CHEX) over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at OMi M 1 Size (M12), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = OMi M 2 Size (M9, crossing to the nut face), nose tip at OMi M 1 Size (M12, crossing to the nose tip); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BL25" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-L-16-16 dims are NOT assumed; confirm before modelling | FOLDS 2026-10-02: filled from OMi Items row 1940; Brennan TFA catalog p34 (same source) differs only in the last printed digit (the catalog cuts OMi M 1 to 2 decimals, QA_Log #158; 9/16 = 0.5625 printed 0.562 / 0.563): M12 OMi 4.406 vs catalog 4.40 | 6500-L row folded into the 6500 master: Brennan 6500-L-08-08-FG STEP (pilot) = 6500-08-08-FG with the forged swivel hex arm 1.430 longer (Q-NEW-FOLD-6500L, 2026-10-02) | hex A/F raised from OMi Hex Flat 1.312 to 1.3125 (JIC thread major; 2603HX rule)</t>
+        </is>
+      </c>
+      <c r="BM25" t="inlineStr">
+        <is>
+          <t>6500-L-16-16-FG</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_6500_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6500_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM25"/>
+  <dimension ref="A1:BM27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -823,7 +823,7 @@
         <v>0.481</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="AC2" t="n">
         <v>0.4225</v>
@@ -941,12 +941,12 @@
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); LEG_M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1926 = 1.18 (table had 1.19) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs) | hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule)</t>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | A19 (user 2026-10-18, group 2 settled): LEG_M10@DRIVE 1.19 -&gt; OMi 1.18 (Items!N1926, M113) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs) | hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule)</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1474,7 +1474,7 @@
         <v>0.218</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="AC5" t="n">
         <v>0.175</v>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); LEG_M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1914 = 0.68 (table had 0.69) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs) | leg 2: the corner puck (radius 0.323) reaches 0.009 past the swivel body face (0.314) but stays inside the neck (max 0.077 off the axis vs neck radius 0.178) - as on the Brennan 6502-08-08-FG / 1503-08-08-FG forgings; leg 2 hex arm 0.314 barely clears the corner puck (radius 0.323)</t>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | A19 (user 2026-10-18, group 2 settled): LEG_M10@DRIVE 0.69 -&gt; OMi 0.68 (Items!N1914, M113) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs) | leg 2: the corner puck (radius 0.323) reaches 0.009 past the swivel body face (0.314) but stays inside the neck (max 0.077 off the axis vs neck radius 0.178) - as on the Brennan 6502-08-08-FG / 1503-08-08-FG forgings; leg 2 hex arm 0.314 barely clears the corner puck (radius 0.323)</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs)</t>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on LEG_M10@DRIVE=0.96~0.96; LEG_M5@DRIVE=1.38~1.38; LEG_M@DRIVE=1.14~1.14; Y@REF=0.75~0.750; HEXB@HEX=0.88~0.875; D1@BORE=0.3~0.297; D2@BORE=0.39~0.391 | DataStatus VERIFIED -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs)</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -2260,14 +2260,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6500-08-10-FG</t>
+          <t>6500-08-06-FG</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="C9" t="n">
-        <v>0.44</v>
+        <v>0.375</v>
       </c>
       <c r="D9" t="n">
         <v>0.375</v>
@@ -2294,76 +2294,76 @@
         <v>37</v>
       </c>
       <c r="L9" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="M9" t="n">
-        <v>0.44</v>
+        <v>0.375</v>
       </c>
       <c r="N9" t="n">
-        <v>0.985</v>
+        <v>0.785</v>
       </c>
       <c r="O9" t="n">
-        <v>0.347</v>
+        <v>0.206</v>
       </c>
       <c r="P9" t="n">
-        <v>0.944</v>
+        <v>0.735</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4758</v>
+        <v>0.3224</v>
       </c>
       <c r="R9" t="n">
-        <v>0.19</v>
+        <v>0.145</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4988</v>
+        <v>0.3428</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5265</v>
+        <v>0.3876</v>
       </c>
       <c r="U9" t="n">
-        <v>0.57735</v>
+        <v>0.39837</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="W9" t="n">
-        <v>0.39884</v>
+        <v>0.25118</v>
       </c>
       <c r="X9" t="n">
-        <v>0.404</v>
+        <v>0.2945</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4475</v>
+        <v>0.2925</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.7794</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.394</v>
+        <v>0.246</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.5</v>
+        <v>0.37</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.3375</v>
+        <v>0.215</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.5265</v>
+        <v>0.3876</v>
       </c>
       <c r="AF9" t="n">
         <v>0.39</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.48</v>
+        <v>0.3</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="AJ9" t="n">
         <v>0.75</v>
@@ -2384,58 +2384,58 @@
         <v>0.0625</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.7976799999999999</v>
+        <v>0.50236</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.4364</v>
+        <v>0.3197</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.39884</v>
+        <v>0.25118</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.673</v>
+        <v>0.593</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.635</v>
+        <v>0.495</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.44</v>
+        <v>0.375</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.44</v>
+        <v>0.375</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.25353</v>
+        <v>0.21601</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.25353</v>
+        <v>0.21601</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.50757</v>
+        <v>0.43251</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>6500-08-10-FG</t>
+          <t>6500-08-06-FG</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 3/4-16 JIC x 7/8-14 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 3/4-16 JIC x 9/16-18 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>7/8-14 (female 37deg JIC swivel)</t>
+          <t>9/16-18 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -2465,26 +2465,26 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs)</t>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p034-t01: agrees on LEG_M@DRIVE, HEXB@HEX, Y@REF, D1@BORE, D2@BORE | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): LEG_M5@DRIVE 1.33 -&gt; 1.28 | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): LEG_M10@DRIVE 0.95 -&gt; 0.91 | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): $PRP@DataStatus VERIFIED -&gt; ASSUMED</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>6500-08-10-FG</t>
+          <t>6500-08-06-FG</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6500-08-12-FG</t>
+          <t>6500-08-08-FG</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="C10" t="n">
-        <v>0.531</v>
+        <v>0.375</v>
       </c>
       <c r="D10" t="n">
         <v>0.375</v>
@@ -2511,76 +2511,76 @@
         <v>37</v>
       </c>
       <c r="L10" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="M10" t="n">
-        <v>0.531</v>
+        <v>0.375</v>
       </c>
       <c r="N10" t="n">
-        <v>1.089</v>
+        <v>0.885</v>
       </c>
       <c r="O10" t="n">
-        <v>0.417</v>
+        <v>0.292</v>
       </c>
       <c r="P10" t="n">
-        <v>1.047</v>
+        <v>0.827</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5928</v>
+        <v>0.4108</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6237</v>
+        <v>0.4361</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5998</v>
+        <v>0.4499</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.50807</v>
       </c>
       <c r="V10" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="W10" t="n">
-        <v>0.48614</v>
+        <v>0.34117</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4472</v>
+        <v>0.3283</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.549</v>
+        <v>0.3925</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.8623</v>
+        <v>0.6723</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.481</v>
+        <v>0.34</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.4225</v>
+        <v>0.2825</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>0.88</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.5998</v>
+        <v>0.4499</v>
       </c>
       <c r="AF10" t="n">
         <v>0.39</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.61</v>
+        <v>0.39</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AJ10" t="n">
         <v>0.75</v>
@@ -2601,58 +2601,58 @@
         <v>0.0625</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.97228</v>
+        <v>0.6823399999999999</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.4851</v>
+        <v>0.3567</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.48614</v>
+        <v>0.34117</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.062</v>
+        <v>0.75</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.763</v>
+        <v>0.593</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.062</v>
+        <v>0.75</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.661</v>
+        <v>0.495</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.531</v>
+        <v>0.375</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.531</v>
+        <v>0.375</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.30607</v>
+        <v>0.21601</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.30607</v>
+        <v>0.21601</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.61265</v>
+        <v>0.43251</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>6500-08-12-FG</t>
+          <t>6500-08-08-FG</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 3/4-16 JIC x 1 1/16-12 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 3/4-16 JIC x 3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female 37deg JIC swivel)</t>
+          <t>3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -2677,46 +2677,46 @@
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R1921 Hex Flat = 1.062 (table had 1.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs)</t>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p034-t01: agrees on LEG_M@DRIVE, HEXB@HEX, Y@REF, D1@BORE, D2@BORE | DataStatus VERIFIED -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs)</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>6500-08-12-FG</t>
+          <t>6500-08-08-FG</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6500-10-08-FG</t>
+          <t>6500-08-10-FG</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="C11" t="n">
         <v>0.44</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="E11" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3553</v>
+        <v>0.2837</v>
       </c>
       <c r="G11" t="n">
-        <v>0.386</v>
+        <v>0.3295</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1114</v>
+        <v>0.0984</v>
       </c>
       <c r="I11" t="n">
         <v>0.1546</v>
@@ -2728,124 +2728,124 @@
         <v>37</v>
       </c>
       <c r="L11" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
         <v>0.44</v>
       </c>
       <c r="N11" t="n">
-        <v>0.885</v>
+        <v>0.985</v>
       </c>
       <c r="O11" t="n">
-        <v>0.292</v>
+        <v>0.347</v>
       </c>
       <c r="P11" t="n">
-        <v>0.827</v>
+        <v>0.944</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4108</v>
+        <v>0.4758</v>
       </c>
       <c r="R11" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4361</v>
+        <v>0.4988</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4499</v>
+        <v>0.5265</v>
       </c>
       <c r="U11" t="n">
-        <v>0.50807</v>
+        <v>0.57735</v>
       </c>
       <c r="V11" t="n">
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="W11" t="n">
-        <v>0.34117</v>
+        <v>0.39884</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3283</v>
+        <v>0.404</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.3925</v>
+        <v>0.4475</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.6723</v>
+        <v>0.7794</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.34</v>
+        <v>0.394</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.2825</v>
+        <v>0.3375</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.4499</v>
+        <v>0.5265</v>
       </c>
       <c r="AF11" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH11" t="n">
         <v>0.48</v>
       </c>
-      <c r="AG11" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.39</v>
-      </c>
       <c r="AI11" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="AK11" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.7976799999999999</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.4364</v>
+      </c>
+      <c r="AR11" t="n">
         <v>0.07142999999999999</v>
       </c>
-      <c r="AL11" t="n">
-        <v>0.3553</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.03866</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0.01786</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0.07142999999999999</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0.6823399999999999</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0.3567</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0.0625</v>
-      </c>
       <c r="AS11" t="n">
-        <v>0.34117</v>
+        <v>0.39884</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AV11" t="n">
         <v>0.88</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.673</v>
       </c>
       <c r="AX11" t="n">
         <v>0.88</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.625</v>
+        <v>0.635</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.44</v>
@@ -2864,12 +2864,12 @@
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>6500-10-08-FG</t>
+          <t>6500-08-10-FG</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 7/8-14 JIC x 3/4-16 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 3/4-16 JIC x 7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>7/8-14 JIC</t>
+          <t>3/4-16 JIC</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>3/4-16 (female 37deg JIC swivel)</t>
+          <t>7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -2899,41 +2899,41 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs)</t>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on LEG_M10@DRIVE=1.12~1.12; LEG_M5@DRIVE=1.62~1.62; LEG_M@DRIVE=1.33~1.33; Y@REF=0.88~0.875; HEXB@HEX=1~1.000; D1@BORE=0.39~0.391; D2@BORE=0.48~0.484 | DataStatus VERIFIED -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs)</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>6500-10-08-FG</t>
+          <t>6500-08-10-FG</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6500-10-10-FG</t>
+          <t>6500-08-12-FG</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="C12" t="n">
-        <v>0.44</v>
+        <v>0.531</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="E12" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3553</v>
+        <v>0.2837</v>
       </c>
       <c r="G12" t="n">
-        <v>0.386</v>
+        <v>0.3295</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1114</v>
+        <v>0.0984</v>
       </c>
       <c r="I12" t="n">
         <v>0.1546</v>
@@ -2945,148 +2945,148 @@
         <v>37</v>
       </c>
       <c r="L12" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="M12" t="n">
-        <v>0.44</v>
+        <v>0.531</v>
       </c>
       <c r="N12" t="n">
-        <v>0.985</v>
+        <v>1.089</v>
       </c>
       <c r="O12" t="n">
-        <v>0.347</v>
+        <v>0.417</v>
       </c>
       <c r="P12" t="n">
-        <v>0.944</v>
+        <v>1.047</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4758</v>
+        <v>0.5928</v>
       </c>
       <c r="R12" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4988</v>
+        <v>0.6237</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5265</v>
+        <v>0.5998</v>
       </c>
       <c r="U12" t="n">
-        <v>0.57735</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4375</v>
+        <v>0.53125</v>
       </c>
       <c r="W12" t="n">
-        <v>0.39884</v>
+        <v>0.48614</v>
       </c>
       <c r="X12" t="n">
-        <v>0.404</v>
+        <v>0.4472</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.4475</v>
+        <v>0.549</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.7794</v>
+        <v>0.8623</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.394</v>
+        <v>0.481</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.3375</v>
+        <v>0.4225</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.5265</v>
+        <v>0.5998</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.48</v>
+        <v>0.39</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.48</v>
+        <v>0.61</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.3553</v>
+        <v>0.2837</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.03866</v>
+        <v>0.03383</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.01786</v>
+        <v>0.01562</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.7976799999999999</v>
+        <v>0.97228</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.4364</v>
+        <v>0.4851</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.08333</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.39884</v>
+        <v>0.48614</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.4375</v>
+        <v>0.53125</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.88</v>
+        <v>1.062</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.763</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.88</v>
+        <v>1.062</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.635</v>
+        <v>0.661</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.44</v>
+        <v>0.531</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.44</v>
+        <v>0.531</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.25353</v>
+        <v>0.30607</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.25353</v>
+        <v>0.30607</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.50757</v>
+        <v>0.61265</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>6500-10-10-FG</t>
+          <t>6500-08-12-FG</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 7/8-14 JIC x 7/8-14 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 3/4-16 JIC x 1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -3096,12 +3096,12 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>7/8-14 JIC</t>
+          <t>3/4-16 JIC</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>7/8-14 (female 37deg JIC swivel)</t>
+          <t>1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -3111,31 +3111,31 @@
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R1921 Hex Flat = 1.062 (table had 1.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs)</t>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs)</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>6500-10-10-FG</t>
+          <t>6500-08-12-FG</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6500-10-12-FG</t>
+          <t>6500-10-08-FG</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="C13" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="D13" t="n">
         <v>0.4375</v>
@@ -3162,76 +3162,76 @@
         <v>37</v>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="M13" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="N13" t="n">
-        <v>1.089</v>
+        <v>0.885</v>
       </c>
       <c r="O13" t="n">
-        <v>0.417</v>
+        <v>0.292</v>
       </c>
       <c r="P13" t="n">
-        <v>1.047</v>
+        <v>0.827</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5928</v>
+        <v>0.4108</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6237</v>
+        <v>0.4361</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5998</v>
+        <v>0.4499</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.50807</v>
       </c>
       <c r="V13" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="W13" t="n">
-        <v>0.48614</v>
+        <v>0.34117</v>
       </c>
       <c r="X13" t="n">
-        <v>0.4472</v>
+        <v>0.3283</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.549</v>
+        <v>0.3925</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.8623</v>
+        <v>0.6723</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.481</v>
+        <v>0.34</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.4225</v>
+        <v>0.2825</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>0.88</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.5998</v>
+        <v>0.4499</v>
       </c>
       <c r="AF13" t="n">
         <v>0.48</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.61</v>
+        <v>0.39</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="AJ13" t="n">
         <v>0.875</v>
@@ -3252,58 +3252,58 @@
         <v>0.07142999999999999</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.97228</v>
+        <v>0.6823399999999999</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.4851</v>
+        <v>0.3567</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.48614</v>
+        <v>0.34117</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.782</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.661</v>
+        <v>0.625</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.3055</v>
+        <v>0.25353</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.3055</v>
+        <v>0.25353</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.61149</v>
+        <v>0.50757</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>6500-10-12-FG</t>
+          <t>6500-10-08-FG</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 7/8-14 JIC x 1 1/16-12 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 7/8-14 JIC x 3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female 37deg JIC swivel)</t>
+          <t>3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -3333,44 +3333,44 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs)</t>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on LEG_M10@DRIVE=1.09~1.09; LEG_M5@DRIVE=1.51~1.51; LEG_M@DRIVE=1.45~1.45; Y@REF=0.88~0.875; HEXB@HEX=0.88~0.875; D1@BORE=0.48~0.484; D2@BORE=0.39~0.391 | DataStatus VERIFIED -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs)</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>6500-10-12-FG</t>
+          <t>6500-10-08-FG</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6500-12-08-FG</t>
+          <t>6500-10-10-FG</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="C14" t="n">
-        <v>0.53125</v>
+        <v>0.44</v>
       </c>
       <c r="D14" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="E14" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3895</v>
+        <v>0.3553</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4715</v>
+        <v>0.386</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1299</v>
+        <v>0.1114</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="J14" t="n">
         <v>60</v>
@@ -3379,148 +3379,148 @@
         <v>37</v>
       </c>
       <c r="L14" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
-        <v>0.53125</v>
+        <v>0.44</v>
       </c>
       <c r="N14" t="n">
-        <v>0.885</v>
+        <v>0.985</v>
       </c>
       <c r="O14" t="n">
-        <v>0.292</v>
+        <v>0.347</v>
       </c>
       <c r="P14" t="n">
-        <v>0.827</v>
+        <v>0.944</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.4108</v>
+        <v>0.4758</v>
       </c>
       <c r="R14" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4361</v>
+        <v>0.4988</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4499</v>
+        <v>0.5265</v>
       </c>
       <c r="U14" t="n">
-        <v>0.50518</v>
+        <v>0.57735</v>
       </c>
       <c r="V14" t="n">
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="W14" t="n">
-        <v>0.34117</v>
+        <v>0.39884</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3283</v>
+        <v>0.404</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.3925</v>
+        <v>0.4475</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.6723</v>
+        <v>0.7794</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.34</v>
+        <v>0.394</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.2825</v>
+        <v>0.3375</v>
       </c>
       <c r="AD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.5265</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>0.875</v>
       </c>
-      <c r="AE14" t="n">
-        <v>0.4499</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0.609</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0.391</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.0625</v>
-      </c>
       <c r="AK14" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.3895</v>
+        <v>0.3553</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.6823399999999999</v>
+        <v>0.7976799999999999</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.3567</v>
+        <v>0.4364</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.0625</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.34117</v>
+        <v>0.39884</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.0625</v>
+        <v>0.88</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.796</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.0625</v>
+        <v>0.88</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.665</v>
+        <v>0.635</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.53125</v>
+        <v>0.44</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.53125</v>
+        <v>0.44</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.30622</v>
+        <v>0.25353</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.30622</v>
+        <v>0.25353</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.61293</v>
+        <v>0.50757</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>6500-12-08-FG</t>
+          <t>6500-10-10-FG</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 1 1/16-12 JIC x 3/4-16 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 7/8-14 JIC x 7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>1 1/16-12 JIC</t>
+          <t>7/8-14 JIC</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>3/4-16 (female 37deg JIC swivel)</t>
+          <t>7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -3545,49 +3545,49 @@
       </c>
       <c r="BK14" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-12-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied; 2026-10-09 (left out of batch 15, staged): LEG_M@DRIVE: OMi Items row 1925 L 1 Size = 1.66; LEG_M5@DRIVE: OMi Items row 1925 M 2 Size = 1.55; LEG_M10@DRIVE: OMi Items row 1925 M 1 Size = 1.13; HEXB@HEX: OMi Items row 1925 Nut Hex 1 = 0.875; Y@REF: OMi Items row 1925 Hex Flat = 1.062; D1@BORE: OMi Items row 1925 Side 1 ID = 0.609; D2@BORE: OMi Items row 1925 Side 2 ID = 0.391; THDMAJ_A@DRIVE: 1 1/16-12 -&gt; 1.0625 (end library); THDMAJ_B@DRIVE: 3/4-16 -&gt; 0.75 (end library) [user 2026-09-25: OMi dims &gt; Air-Way; user 2026-10-08: no size from Brennan alone -&gt; OMi stands, ASSUMED]; pairing: OMi L 1 = male JIC leg (catalog M), M 2 = swivel-nut face (M6), M 1 = swivel nose / seat (M4), Hex Flat = body hex, Nut Hex 1 = swivel nut hex, Side 1 / 2 ID = bores of ends 1 / 2 (batch-15 pairing, Brennan TFA p34 letters) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-12-08 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-09 (staged): this part's own sizes from OMi WebsitePartsInfo2026 Items row 1925 - ASSUMED (one source). It was held in batch 15 because the Brennan TFA catalog prints other values for it; under the 2026-10-08 ruling the catalog (= OMi's source) is evidence only and OMi stands. Catalog print for the record: TFA-p034-t01: TUBE O.D. 3/4, B1 SAE 37Deg 1-1/16-12, B2 SAE 37Deg 3/4-16, B1 DRILL 0.609, B2 DRILL 0.391, M LGTH 1.660, M4 LGTH 1.120, M6 LGTH 1.550, C HEX 0.875, Y FLATS 1.062 | hex A/F raised from Air-Way 1.062 to 1.0625 (JIC thread major; 2603HX rule)</t>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs)</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>6500-12-08-FG</t>
+          <t>6500-10-10-FG</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6500-12-16-FG</t>
+          <t>6500-10-12-FG</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="C15" t="n">
-        <v>0.656</v>
+        <v>0.53</v>
       </c>
       <c r="D15" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="E15" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3895</v>
+        <v>0.3553</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4715</v>
+        <v>0.386</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1299</v>
+        <v>0.1114</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="J15" t="n">
         <v>60</v>
@@ -3596,148 +3596,148 @@
         <v>37</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="M15" t="n">
-        <v>0.656</v>
+        <v>0.53</v>
       </c>
       <c r="N15" t="n">
-        <v>1.175</v>
+        <v>1.089</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5485</v>
+        <v>0.417</v>
       </c>
       <c r="P15" t="n">
-        <v>1.139</v>
+        <v>1.047</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.727</v>
+        <v>0.5928</v>
       </c>
       <c r="R15" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="S15" t="n">
-        <v>0.749</v>
+        <v>0.6237</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6564</v>
+        <v>0.5998</v>
       </c>
       <c r="U15" t="n">
-        <v>0.86603</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="W15" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="X15" t="n">
-        <v>0.4873</v>
+        <v>0.4472</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.665</v>
+        <v>0.549</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.9544</v>
+        <v>0.8623</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.604</v>
+        <v>0.481</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.5475</v>
+        <v>0.4225</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.6564</v>
+        <v>0.5998</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.609</v>
+        <v>0.48</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.844</v>
+        <v>0.61</v>
       </c>
       <c r="AI15" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.3895</v>
+        <v>0.3553</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.22228</v>
+        <v>0.97228</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.5252</v>
+        <v>0.4851</v>
       </c>
       <c r="AR15" t="n">
         <v>0.08333</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="AU15" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.312</v>
+        <v>1.06</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.896</v>
+        <v>0.782</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.312</v>
+        <v>1.06</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.825</v>
+        <v>0.661</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.656</v>
+        <v>0.53</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.656</v>
+        <v>0.53</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.37824</v>
+        <v>0.3055</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.37824</v>
+        <v>0.3055</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.75698</v>
+        <v>0.61149</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>6500-12-16-FG</t>
+          <t>6500-10-12-FG</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 1 1/16-12 JIC x 1 5/16-12 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 7/8-14 JIC x 1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>1 1/16-12 JIC</t>
+          <t>7/8-14 JIC</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female 37deg JIC swivel)</t>
+          <t>1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -3762,49 +3762,49 @@
       </c>
       <c r="BK15" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-12-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied; 2026-10-09 (left out of batch 15, staged): LEG_M@DRIVE: OMi Items row 1927 L 1 Size = 1.76; LEG_M5@DRIVE: OMi Items row 1927 M 2 Size = 2.00; LEG_M10@DRIVE: OMi Items row 1927 M 1 Size = 1.41; HEXB@HEX: OMi Items row 1927 Nut Hex 1 = 1.500; Y@REF: OMi Items row 1927 Hex Flat = 1.312; D1@BORE: OMi Items row 1927 Side 1 ID = 0.609; D2@BORE: OMi Items row 1927 Side 2 ID = 0.844; THDMAJ_A@DRIVE: 1 1/16-12 -&gt; 1.0625 (end library); THDMAJ_B@DRIVE: 1 5/16-12 -&gt; 1.3125 (end library) [user 2026-09-25: OMi dims &gt; Air-Way; user 2026-10-08: no size from Brennan alone -&gt; OMi stands, ASSUMED]; pairing: OMi L 1 = male JIC leg (catalog M), M 2 = swivel-nut face (M6), M 1 = swivel nose / seat (M4), Hex Flat = body hex, Nut Hex 1 = swivel nut hex, Side 1 / 2 ID = bores of ends 1 / 2 (batch-15 pairing, Brennan TFA p34 letters) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); LEG_M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1924 = 1.18 (table had 1.19) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-12-16 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-09 (staged): this part's own sizes from OMi WebsitePartsInfo2026 Items row 1927 - ASSUMED (one source). It was held in batch 15 because the Brennan TFA catalog prints other values for it; under the 2026-10-08 ruling the catalog (= OMi's source) is evidence only and OMi stands. Catalog print for the record: TFA-p034-t01: TUBE O.D. 3/4, B1 SAE 37Deg 1-1/16-12, B2 SAE 37Deg 1-5/16-12, B1 DRILL 0.609, B2 DRILL 0.844, M LGTH 1.81, M4 LGTH 1.40, M6 LGTH 2.00, C HEX 1.500, Y FLATS 1.312</t>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | A19 (user 2026-10-18, group 2 settled): LEG_M10@DRIVE 1.19 -&gt; OMi 1.18 (Items!N1924, M113)</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>6500-12-16-FG</t>
+          <t>6500-10-12-FG</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6500-16-12-FG</t>
+          <t>6500-12-08-FG</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="C16" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="D16" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="E16" t="n">
         <v>0.125</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5965</v>
+        <v>0.4715</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="J16" t="n">
         <v>60</v>
@@ -3813,85 +3813,85 @@
         <v>37</v>
       </c>
       <c r="L16" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="M16" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="N16" t="n">
-        <v>1.089</v>
+        <v>0.885</v>
       </c>
       <c r="O16" t="n">
-        <v>0.417</v>
+        <v>0.292</v>
       </c>
       <c r="P16" t="n">
-        <v>1.047</v>
+        <v>0.827</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.5928</v>
+        <v>0.4108</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6237</v>
+        <v>0.4361</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5998</v>
+        <v>0.4499</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.50518</v>
       </c>
       <c r="V16" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="W16" t="n">
-        <v>0.48614</v>
+        <v>0.34117</v>
       </c>
       <c r="X16" t="n">
-        <v>0.4472</v>
+        <v>0.3283</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.549</v>
+        <v>0.3925</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.8623</v>
+        <v>0.6723</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.481</v>
+        <v>0.34</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.4225</v>
+        <v>0.2825</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>0.875</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.5998</v>
+        <v>0.4499</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.844</v>
+        <v>0.609</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.609</v>
+        <v>0.391</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="AK16" t="n">
         <v>0.08333</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="AM16" t="n">
         <v>0.04511</v>
@@ -3903,58 +3903,58 @@
         <v>0.08333</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.97228</v>
+        <v>0.6823399999999999</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.4851</v>
+        <v>0.3567</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.48614</v>
+        <v>0.34117</v>
       </c>
       <c r="AT16" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>0.53125</v>
       </c>
-      <c r="AU16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>1.3125</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0.899</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.3125</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0.861</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0.65625</v>
-      </c>
       <c r="BA16" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.37839</v>
+        <v>0.30622</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.37839</v>
+        <v>0.30622</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.75727</v>
+        <v>0.61293</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>6500-16-12-FG</t>
+          <t>6500-12-08-FG</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 1 5/16-12 JIC x 1 1/16-12 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 1 1/16-12 JIC x 3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>1 5/16-12 JIC</t>
+          <t>1 1/16-12 JIC</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female 37deg JIC swivel)</t>
+          <t>3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -3979,49 +3979,49 @@
       </c>
       <c r="BK16" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-16-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied; 2026-10-09 (left out of batch 15, staged): LEG_M@DRIVE: OMi Items row 1928 L 1 Size = 1.81; LEG_M5@DRIVE: OMi Items row 1928 M 2 Size = 1.95; LEG_M10@DRIVE: OMi Items row 1928 M 1 Size = 1.39; HEXB@HEX: OMi Items row 1928 Nut Hex 1 = 1.250; Y@REF: OMi Items row 1928 Hex Flat = 1.312; D1@BORE: OMi Items row 1928 Side 1 ID = 0.844; D2@BORE: OMi Items row 1928 Side 2 ID = 0.609; THDMAJ_A@DRIVE: 1 5/16-12 -&gt; 1.3125 (end library); THDMAJ_B@DRIVE: 1 1/16-12 -&gt; 1.0625 (end library) [user 2026-09-25: OMi dims &gt; Air-Way; user 2026-10-08: no size from Brennan alone -&gt; OMi stands, ASSUMED]; pairing: OMi L 1 = male JIC leg (catalog M), M 2 = swivel-nut face (M6), M 1 = swivel nose / seat (M4), Hex Flat = body hex, Nut Hex 1 = swivel nut hex, Side 1 / 2 ID = bores of ends 1 / 2 (batch-15 pairing, Brennan TFA p34 letters) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-12-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied; 2026-10-09 (left out of batch 15, staged): LEG_M@DRIVE: OMi Items row 1925 L 1 Size = 1.66; LEG_M5@DRIVE: OMi Items row 1925 M 2 Size = 1.55; LEG_M10@DRIVE: OMi Items row 1925 M 1 Size = 1.13; HEXB@HEX: OMi Items row 1925 Nut Hex 1 = 0.875; Y@REF: OMi Items row 1925 Hex Flat = 1.062; D1@BORE: OMi Items row 1925 Side 1 ID = 0.609; D2@BORE: OMi Items row 1925 Side 2 ID = 0.391; THDMAJ_A@DRIVE: 1 1/16-12 -&gt; 1.0625 (end library); THDMAJ_B@DRIVE: 3/4-16 -&gt; 0.75 (end library) [user 2026-09-25: OMi dims &gt; Air-Way; user 2026-10-08: no size from Brennan alone -&gt; OMi stands, ASSUMED]; pairing: OMi L 1 = male JIC leg (catalog M), M 2 = swivel-nut face (M6), M 1 = swivel nose / seat (M4), Hex Flat = body hex, Nut Hex 1 = swivel nut hex, Side 1 / 2 ID = bores of ends 1 / 2 (batch-15 pairing, Brennan TFA p34 letters) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-16-12 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-09 (staged): this part's own sizes from OMi WebsitePartsInfo2026 Items row 1928 - ASSUMED (one source). It was held in batch 15 because the Brennan TFA catalog prints other values for it; under the 2026-10-08 ruling the catalog (= OMi's source) is evidence only and OMi stands. Catalog print for the record: TFA-p034-t01: TUBE O.D. 1, B1 SAE 37Deg 1-5/16-12, B2 SAE 37Deg 1-1/16-12, B1 DRILL 0.844, B2 DRILL 0.609, M LGTH 1.81, M4 LGTH 1.34, M6 LGTH 1.91, C HEX 1.250, Y FLATS 1.312 | hex A/F raised from Air-Way 1.312 to 1.3125 (JIC thread major; 2603HX rule)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-12-08 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-09 (staged): this part's own sizes from OMi WebsitePartsInfo2026 Items row 1925 - ASSUMED (one source). It was held in batch 15 because the Brennan TFA catalog prints other values for it; under the 2026-10-08 ruling the catalog (= OMi's source) is evidence only and OMi stands. Catalog print for the record: TFA-p034-t01: TUBE O.D. 3/4, B1 SAE 37Deg 1-1/16-12, B2 SAE 37Deg 3/4-16, B1 DRILL 0.609, B2 DRILL 0.391, M LGTH 1.660, M4 LGTH 1.120, M6 LGTH 1.550, C HEX 0.875, Y FLATS 1.062 | hex A/F raised from Air-Way 1.062 to 1.0625 (JIC thread major; 2603HX rule)</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>6500-16-12-FG</t>
+          <t>6500-12-08-FG</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6500-16-16-FG</t>
+          <t>6500-12-16-FG</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="C17" t="n">
-        <v>0.65625</v>
+        <v>0.656</v>
       </c>
       <c r="D17" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="E17" t="n">
         <v>0.125</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5965</v>
+        <v>0.4715</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="J17" t="n">
         <v>60</v>
@@ -4033,7 +4033,7 @@
         <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>0.65625</v>
+        <v>0.656</v>
       </c>
       <c r="N17" t="n">
         <v>1.175</v>
@@ -4090,25 +4090,25 @@
         <v>0.6564</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.84</v>
+        <v>0.609</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.84</v>
+        <v>0.844</v>
       </c>
       <c r="AI17" t="n">
         <v>2</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="AK17" t="n">
         <v>0.08333</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="AM17" t="n">
         <v>0.04511</v>
@@ -4138,40 +4138,40 @@
         <v>2</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.3125</v>
+        <v>1.312</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.899</v>
+        <v>0.896</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.3125</v>
+        <v>1.312</v>
       </c>
       <c r="AY17" t="n">
         <v>0.825</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.65625</v>
+        <v>0.656</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.65625</v>
+        <v>0.656</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.37839</v>
+        <v>0.37824</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.37839</v>
+        <v>0.37824</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.75727</v>
+        <v>0.75698</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>6500-16-16-FG</t>
+          <t>6500-12-16-FG</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 1 5/16-12 JIC x 1 5/16-12 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 1 1/16-12 JIC x 1 5/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>1 5/16-12 JIC</t>
+          <t>1 1/16-12 JIC</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -4196,49 +4196,49 @@
       </c>
       <c r="BK17" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-12-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied; 2026-10-09 (left out of batch 15, staged): LEG_M@DRIVE: OMi Items row 1927 L 1 Size = 1.76; LEG_M5@DRIVE: OMi Items row 1927 M 2 Size = 2.00; LEG_M10@DRIVE: OMi Items row 1927 M 1 Size = 1.41; HEXB@HEX: OMi Items row 1927 Nut Hex 1 = 1.500; Y@REF: OMi Items row 1927 Hex Flat = 1.312; D1@BORE: OMi Items row 1927 Side 1 ID = 0.609; D2@BORE: OMi Items row 1927 Side 2 ID = 0.844; THDMAJ_A@DRIVE: 1 1/16-12 -&gt; 1.0625 (end library); THDMAJ_B@DRIVE: 1 5/16-12 -&gt; 1.3125 (end library) [user 2026-09-25: OMi dims &gt; Air-Way; user 2026-10-08: no size from Brennan alone -&gt; OMi stands, ASSUMED]; pairing: OMi L 1 = male JIC leg (catalog M), M 2 = swivel-nut face (M6), M 1 = swivel nose / seat (M4), Hex Flat = body hex, Nut Hex 1 = swivel nut hex, Side 1 / 2 ID = bores of ends 1 / 2 (batch-15 pairing, Brennan TFA p34 letters) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>legs differ from MS51521: AW M=1.81/M5=2.0 vs MS 1.8/2.0; RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-12-16 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-09 (staged): this part's own sizes from OMi WebsitePartsInfo2026 Items row 1927 - ASSUMED (one source). It was held in batch 15 because the Brennan TFA catalog prints other values for it; under the 2026-10-08 ruling the catalog (= OMi's source) is evidence only and OMi stands. Catalog print for the record: TFA-p034-t01: TUBE O.D. 3/4, B1 SAE 37Deg 1-1/16-12, B2 SAE 37Deg 1-5/16-12, B1 DRILL 0.609, B2 DRILL 0.844, M LGTH 1.81, M4 LGTH 1.40, M6 LGTH 2.00, C HEX 1.500, Y FLATS 1.312</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>6500-16-16-FG</t>
+          <t>6500-12-16-FG</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6500-20-20-FG</t>
+          <t>6500-16-12-FG</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="E18" t="n">
         <v>0.125</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="G18" t="n">
-        <v>0.753</v>
+        <v>0.5965</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="J18" t="n">
         <v>60</v>
@@ -4247,85 +4247,85 @@
         <v>37</v>
       </c>
       <c r="L18" t="n">
-        <v>2.31</v>
+        <v>1.95</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="N18" t="n">
-        <v>1.26</v>
+        <v>1.089</v>
       </c>
       <c r="O18" t="n">
-        <v>0.68</v>
+        <v>0.417</v>
       </c>
       <c r="P18" t="n">
-        <v>1.145</v>
+        <v>1.047</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.949</v>
+        <v>0.5928</v>
       </c>
       <c r="R18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9889</v>
+        <v>0.6237</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5375</v>
+        <v>0.5998</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1547</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8125</v>
+        <v>0.53125</v>
       </c>
       <c r="W18" t="n">
-        <v>0.76739</v>
+        <v>0.48614</v>
       </c>
       <c r="X18" t="n">
-        <v>0.4345</v>
+        <v>0.4472</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.88</v>
+        <v>0.549</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.9556</v>
+        <v>0.8623</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.766</v>
+        <v>0.481</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.7025</v>
+        <v>0.4225</v>
       </c>
       <c r="AD18" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.5375</v>
+        <v>0.5998</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.08</v>
+        <v>0.844</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.08</v>
+        <v>0.609</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.31</v>
+        <v>1.95</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="AK18" t="n">
         <v>0.08333</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="AM18" t="n">
         <v>0.04511</v>
@@ -4337,58 +4337,58 @@
         <v>0.08333</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.53478</v>
+        <v>0.97228</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.4724</v>
+        <v>0.4851</v>
       </c>
       <c r="AR18" t="n">
         <v>0.08333</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.76739</v>
+        <v>0.48614</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.8125</v>
+        <v>0.53125</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.31</v>
+        <v>1.95</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.102</v>
+        <v>0.899</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.05</v>
+        <v>0.861</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="BB18" t="n">
-        <v>0.4686</v>
+        <v>0.37839</v>
       </c>
       <c r="BC18" t="n">
-        <v>0.4686</v>
+        <v>0.37839</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.93769</v>
+        <v>0.75727</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>6500-20-20-FG</t>
+          <t>6500-16-12-FG</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 1 5/8-12 JIC x 1 5/8-12 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 1 5/16-12 JIC x 1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>1 5/8-12 JIC</t>
+          <t>1 5/16-12 JIC</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>1 5/8-12 (female 37deg JIC swivel)</t>
+          <t>1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -4413,49 +4413,49 @@
       </c>
       <c r="BK18" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-16-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied; 2026-10-09 (left out of batch 15, staged): LEG_M@DRIVE: OMi Items row 1928 L 1 Size = 1.81; LEG_M5@DRIVE: OMi Items row 1928 M 2 Size = 1.95; LEG_M10@DRIVE: OMi Items row 1928 M 1 Size = 1.39; HEXB@HEX: OMi Items row 1928 Nut Hex 1 = 1.250; Y@REF: OMi Items row 1928 Hex Flat = 1.312; D1@BORE: OMi Items row 1928 Side 1 ID = 0.844; D2@BORE: OMi Items row 1928 Side 2 ID = 0.609; THDMAJ_A@DRIVE: 1 5/16-12 -&gt; 1.3125 (end library); THDMAJ_B@DRIVE: 1 1/16-12 -&gt; 1.0625 (end library) [user 2026-09-25: OMi dims &gt; Air-Way; user 2026-10-08: no size from Brennan alone -&gt; OMi stands, ASSUMED]; pairing: OMi L 1 = male JIC leg (catalog M), M 2 = swivel-nut face (M6), M 1 = swivel nose / seat (M4), Hex Flat = body hex, Nut Hex 1 = swivel nut hex, Side 1 / 2 ID = bores of ends 1 / 2 (batch-15 pairing, Brennan TFA p34 letters) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs) | hex A/F raised from Air-Way 1.62 to 1.6250 (JIC thread major; 2603HX rule); leg 2: Air-Way nut-face-to-seat 0.620 vs Brennan 0.640</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-16-12 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-09 (staged): this part's own sizes from OMi WebsitePartsInfo2026 Items row 1928 - ASSUMED (one source). It was held in batch 15 because the Brennan TFA catalog prints other values for it; under the 2026-10-08 ruling the catalog (= OMi's source) is evidence only and OMi stands. Catalog print for the record: TFA-p034-t01: TUBE O.D. 1, B1 SAE 37Deg 1-5/16-12, B2 SAE 37Deg 1-1/16-12, B1 DRILL 0.844, B2 DRILL 0.609, M LGTH 1.81, M4 LGTH 1.34, M6 LGTH 1.91, C HEX 1.250, Y FLATS 1.312 | hex A/F raised from Air-Way 1.312 to 1.3125 (JIC thread major; 2603HX rule)</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>6500-20-20-FG</t>
+          <t>6500-16-12-FG</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6500-24-24-FG</t>
+          <t>6500-16-16-FG</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.33</v>
+        <v>1.81</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9375</v>
+        <v>0.65625</v>
       </c>
       <c r="E19" t="n">
         <v>0.125</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5454</v>
+        <v>0.4365</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.5965</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1298</v>
+        <v>0.1292</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2482</v>
+        <v>0.1858</v>
       </c>
       <c r="J19" t="n">
         <v>60</v>
@@ -4464,85 +4464,85 @@
         <v>37</v>
       </c>
       <c r="L19" t="n">
-        <v>2.59</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="N19" t="n">
-        <v>1.41</v>
+        <v>1.175</v>
       </c>
       <c r="O19" t="n">
-        <v>0.776</v>
+        <v>0.5485</v>
       </c>
       <c r="P19" t="n">
-        <v>1.32</v>
+        <v>1.139</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.0504</v>
+        <v>0.727</v>
       </c>
       <c r="R19" t="n">
         <v>0.23</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1134</v>
+        <v>0.749</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7063</v>
+        <v>0.6564</v>
       </c>
       <c r="U19" t="n">
-        <v>1.29904</v>
+        <v>0.86603</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9375</v>
+        <v>0.65625</v>
       </c>
       <c r="W19" t="n">
-        <v>0.89239</v>
+        <v>0.61114</v>
       </c>
       <c r="X19" t="n">
-        <v>0.5295</v>
+        <v>0.4873</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.01</v>
+        <v>0.665</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.065</v>
+        <v>0.9544</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.8885</v>
+        <v>0.604</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.73</v>
+        <v>0.59</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.5475</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.7063</v>
+        <v>0.6564</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.31</v>
+        <v>0.84</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.33</v>
+        <v>1.81</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.31</v>
+        <v>0.84</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.59</v>
+        <v>2</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.875</v>
+        <v>1.3125</v>
       </c>
       <c r="AK19" t="n">
         <v>0.08333</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.5454</v>
+        <v>0.4365</v>
       </c>
       <c r="AM19" t="n">
         <v>0.04511</v>
@@ -4554,58 +4554,58 @@
         <v>0.08333</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.78478</v>
+        <v>1.22228</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.5674</v>
+        <v>0.5252</v>
       </c>
       <c r="AR19" t="n">
         <v>0.08333</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.89239</v>
+        <v>0.61114</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.9375</v>
+        <v>0.65625</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.59</v>
+        <v>2</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.88</v>
+        <v>1.3125</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.247</v>
+        <v>0.899</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.88</v>
+        <v>1.3125</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.18</v>
+        <v>0.825</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="BB19" t="n">
-        <v>0.54221</v>
+        <v>0.37839</v>
       </c>
       <c r="BC19" t="n">
-        <v>0.54221</v>
+        <v>0.37839</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.08492</v>
+        <v>0.75727</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>6500-24-24-FG</t>
+          <t>6500-16-16-FG</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 1 7/8-12 JIC x 1 7/8-12 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 1 5/16-12 JIC x 1 5/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>1 7/8-12 JIC</t>
+          <t>1 5/16-12 JIC</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>1 7/8-12 (female 37deg JIC swivel)</t>
+          <t>1 5/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -4635,44 +4635,44 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs)</t>
+          <t>legs differ from MS51521: AW M=1.81/M5=2.0 vs MS 1.8/2.0; RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on LEG_M10@DRIVE=1.41~1.41; LEG_M5@DRIVE=2~2.00; LEG_M@DRIVE=1.81~1.81; Y@REF=1.31~1.312; HEXB@HEX=1.5~1.500; D1@BORE=0.84~0.844; D2@BORE=0.84~0.844 | DataStatus VERIFIED -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs) | hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule)</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>6500-24-24-FG</t>
+          <t>6500-16-16-FG</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6500-32-32-FG</t>
+          <t>6500-20-20-FG</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.06</v>
+        <v>2.06</v>
       </c>
       <c r="C20" t="n">
-        <v>1.25</v>
+        <v>0.8125</v>
       </c>
       <c r="D20" t="n">
-        <v>1.25</v>
+        <v>0.8125</v>
       </c>
       <c r="E20" t="n">
         <v>0.125</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7124</v>
+        <v>0.4316</v>
       </c>
       <c r="G20" t="n">
-        <v>1.19</v>
+        <v>0.753</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1292</v>
+        <v>0.1288</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3318</v>
+        <v>0.2382</v>
       </c>
       <c r="J20" t="n">
         <v>60</v>
@@ -4681,85 +4681,85 @@
         <v>37</v>
       </c>
       <c r="L20" t="n">
-        <v>3.38</v>
+        <v>2.31</v>
       </c>
       <c r="M20" t="n">
-        <v>1.25</v>
+        <v>0.8125</v>
       </c>
       <c r="N20" t="n">
-        <v>1.67</v>
+        <v>1.26</v>
       </c>
       <c r="O20" t="n">
-        <v>1.0785</v>
+        <v>0.68</v>
       </c>
       <c r="P20" t="n">
-        <v>1.61</v>
+        <v>1.145</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.3936</v>
+        <v>0.949</v>
       </c>
       <c r="R20" t="n">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4242</v>
+        <v>0.9889</v>
       </c>
       <c r="T20" t="n">
-        <v>0.862</v>
+        <v>0.5375</v>
       </c>
       <c r="U20" t="n">
-        <v>1.66277</v>
+        <v>1.1547</v>
       </c>
       <c r="V20" t="n">
-        <v>1.25</v>
+        <v>0.8125</v>
       </c>
       <c r="W20" t="n">
-        <v>1.20489</v>
+        <v>0.76739</v>
       </c>
       <c r="X20" t="n">
-        <v>0.702</v>
+        <v>0.4345</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.325</v>
+        <v>0.88</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.4202</v>
+        <v>0.9556</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.198</v>
+        <v>0.766</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.1175</v>
+        <v>0.7025</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.862</v>
+        <v>0.5375</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.78</v>
+        <v>1.08</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.06</v>
+        <v>2.06</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.78</v>
+        <v>1.08</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.38</v>
+        <v>2.31</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.5</v>
+        <v>1.625</v>
       </c>
       <c r="AK20" t="n">
         <v>0.08333</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.7124</v>
+        <v>0.4316</v>
       </c>
       <c r="AM20" t="n">
         <v>0.04511</v>
@@ -4771,58 +4771,58 @@
         <v>0.08333</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.40978</v>
+        <v>1.53478</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.7399</v>
+        <v>0.4724</v>
       </c>
       <c r="AR20" t="n">
         <v>0.08333</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.20489</v>
+        <v>0.76739</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.25</v>
+        <v>0.8125</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.38</v>
+        <v>2.31</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.5</v>
+        <v>1.625</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.727</v>
+        <v>1.102</v>
       </c>
       <c r="AX20" t="n">
-        <v>2.5</v>
+        <v>1.625</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.71</v>
+        <v>1.05</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.25</v>
+        <v>0.8125</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.25</v>
+        <v>0.8125</v>
       </c>
       <c r="BB20" t="n">
-        <v>0.72119</v>
+        <v>0.4686</v>
       </c>
       <c r="BC20" t="n">
-        <v>0.72119</v>
+        <v>0.4686</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.44288</v>
+        <v>0.93769</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>6500-32-32-FG</t>
+          <t>6500-20-20-FG</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 2 1/2-12 JIC x 2 1/2-12 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 1 5/8-12 JIC x 1 5/8-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
@@ -4832,12 +4832,12 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2 1/2-12 JIC</t>
+          <t>1 5/8-12 JIC</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>2 1/2-12 (female 37deg JIC swivel)</t>
+          <t>1 5/8-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
@@ -4852,44 +4852,44 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs)</t>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs) | hex A/F raised from Air-Way 1.62 to 1.6250 (JIC thread major; 2603HX rule); leg 2: Air-Way nut-face-to-seat 0.620 vs Brennan 0.640</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>6500-32-32-FG</t>
+          <t>6500-20-20-FG</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6500-L-04-04-FG</t>
+          <t>6500-24-24-FG</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.89</v>
+        <v>2.33</v>
       </c>
       <c r="C21" t="n">
-        <v>0.219</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>0.21875</v>
+        <v>0.9375</v>
       </c>
       <c r="E21" t="n">
-        <v>0.075</v>
+        <v>0.125</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2608</v>
+        <v>0.5454</v>
       </c>
       <c r="G21" t="n">
-        <v>0.182</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0795</v>
+        <v>0.1298</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1135</v>
+        <v>0.2482</v>
       </c>
       <c r="J21" t="n">
         <v>60</v>
@@ -4898,148 +4898,148 @@
         <v>37</v>
       </c>
       <c r="L21" t="n">
-        <v>2.16</v>
+        <v>2.59</v>
       </c>
       <c r="M21" t="n">
-        <v>0.219</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6850000000000001</v>
+        <v>1.41</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1465</v>
+        <v>0.776</v>
       </c>
       <c r="P21" t="n">
-        <v>0.649</v>
+        <v>1.32</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.2574</v>
+        <v>1.0504</v>
       </c>
       <c r="R21" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2796</v>
+        <v>1.1134</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3268</v>
+        <v>0.7063</v>
       </c>
       <c r="U21" t="n">
-        <v>0.32505</v>
+        <v>1.29904</v>
       </c>
       <c r="V21" t="n">
-        <v>0.21875</v>
+        <v>0.9375</v>
       </c>
       <c r="W21" t="n">
-        <v>0.19169</v>
+        <v>0.89239</v>
       </c>
       <c r="X21" t="n">
-        <v>0.264</v>
+        <v>0.5295</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.235</v>
+        <v>1.01</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.5243</v>
+        <v>1.065</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.1845</v>
+        <v>0.8885</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.344</v>
+        <v>0.73</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.145</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.5629999999999999</v>
+        <v>2.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.3268</v>
+        <v>0.7063</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.172</v>
+        <v>1.31</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.89</v>
+        <v>2.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.172</v>
+        <v>1.31</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.16</v>
+        <v>2.59</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.4375</v>
+        <v>1.875</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.05</v>
+        <v>0.08333</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.2608</v>
+        <v>0.5454</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.02706</v>
+        <v>0.04511</v>
       </c>
       <c r="AN21" t="n">
-        <v>0.0125</v>
+        <v>0.02083</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.05</v>
+        <v>0.08333</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.38338</v>
+        <v>1.78478</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.2867</v>
+        <v>0.5674</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.05</v>
+        <v>0.08333</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.19169</v>
+        <v>0.89239</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.21875</v>
+        <v>0.9375</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.16</v>
+        <v>2.59</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.438</v>
+        <v>1.88</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.34</v>
+        <v>1.247</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.438</v>
+        <v>1.88</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.475</v>
+        <v>1.18</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.219</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BA21" t="n">
-        <v>0.219</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BB21" t="n">
-        <v>0.12594</v>
+        <v>0.54221</v>
       </c>
       <c r="BC21" t="n">
-        <v>0.12594</v>
+        <v>0.54221</v>
       </c>
       <c r="BD21" t="n">
-        <v>0.25238</v>
+        <v>1.08492</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>6500-L-04-04-FG</t>
+          <t>6500-24-24-FG</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 7/16-20 JIC x 7/16-20 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 1 7/8-12 JIC x 1 7/8-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>7/16-20 JIC</t>
+          <t>1 7/8-12 JIC</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>7/16-20 (female 37deg JIC swivel)</t>
+          <t>1 7/8-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
@@ -5064,49 +5064,49 @@
       </c>
       <c r="BK21" t="inlineStr">
         <is>
-          <t>OMi WebsitePartsInfo2026.xlsx Items row 1936 (OMi first, user decision 2026-09-25): M = L 1, M9 = M 2 (crossing to the swivel-nut face), M12 = M 1 (crossing to the nose tip), Y = Hex Flat, CHEX = Nut Hex 1, D1 / D2 = Side 1 / Side 2 ID - column meaning from the Brennan TFA catalog p34 drawing letters (M / M6 / M4 / Y FLATS / C HEX / B1 / B2 DRILL, OMi = catalog 5/5); OMi and Brennan are ONE source -&gt; ASSUMED; male JIC end VERIFIED (MS33656J) | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-L-04-04 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): the forged swivel hex arm runs on to the swivel end of the same size (BRENNAN_6500-L-08-08-FG; its length through the swivel end-library constant SW2_BODYS); the sizes of the part are OMi's | FOLD: 6500-L fold: the extra length is the forged swivel hex arm, the swivel end is the 6500 one of the same size (Brennan 6500-L-08-08-FG STEP, tools/measure/swiv.py + elbow90.py: swivel end = SWIV_MEAS[8], arm 0..1.925 continuous; measured at -08 only, ASSUMED for the other sizes) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(OMi Hex Flat (Y), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = OMi Nut Hex 1 (CHEX) over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at OMi M 1 Size (M12), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = OMi M 2 Size (M9, crossing to the nut face), nose tip at OMi M 1 Size (M12, crossing to the nose tip); each leg bore runs from its face to the axis crossing</t>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-L-04-04 dims are NOT assumed; confirm before modelling | FOLDS 2026-10-02: filled from OMi Items row 1936; Brennan TFA catalog p34 (same source) differs only in the last printed digit (the catalog cuts OMi M 1 to 2 decimals, QA_Log #158; 9/16 = 0.5625 printed 0.562 / 0.563): M12 OMi 1.816 vs catalog 1.81; CHEX OMi 0.563 vs catalog 0.562 | 6500-L row folded into the 6500 master: Brennan 6500-L-08-08-FG STEP (pilot) = 6500-08-08-FG with the forged swivel hex arm 1.430 longer (Q-NEW-FOLD-6500L, 2026-10-02)</t>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs)</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>6500-L-04-04-FG</t>
+          <t>6500-24-24-FG</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6500-L-06-06-FG</t>
+          <t>6500-32-32-FG</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.06</v>
+        <v>3.06</v>
       </c>
       <c r="C22" t="n">
-        <v>0.28125</v>
+        <v>1.25</v>
       </c>
       <c r="D22" t="n">
-        <v>0.28125</v>
+        <v>1.25</v>
       </c>
       <c r="E22" t="n">
-        <v>0.083</v>
+        <v>0.125</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2515</v>
+        <v>0.7124</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2405</v>
+        <v>1.19</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0898</v>
+        <v>0.1292</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1082</v>
+        <v>0.3318</v>
       </c>
       <c r="J22" t="n">
         <v>60</v>
@@ -5115,148 +5115,148 @@
         <v>37</v>
       </c>
       <c r="L22" t="n">
-        <v>2.54</v>
+        <v>3.38</v>
       </c>
       <c r="M22" t="n">
-        <v>0.28125</v>
+        <v>1.25</v>
       </c>
       <c r="N22" t="n">
-        <v>0.785</v>
+        <v>1.67</v>
       </c>
       <c r="O22" t="n">
-        <v>0.206</v>
+        <v>1.0785</v>
       </c>
       <c r="P22" t="n">
-        <v>0.735</v>
+        <v>1.61</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.3224</v>
+        <v>1.3936</v>
       </c>
       <c r="R22" t="n">
-        <v>0.145</v>
+        <v>0.27</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3428</v>
+        <v>1.4242</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3876</v>
+        <v>0.862</v>
       </c>
       <c r="U22" t="n">
-        <v>0.39722</v>
+        <v>1.66277</v>
       </c>
       <c r="V22" t="n">
-        <v>0.28125</v>
+        <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>0.25118</v>
+        <v>1.20489</v>
       </c>
       <c r="X22" t="n">
-        <v>0.2945</v>
+        <v>0.702</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.2925</v>
+        <v>1.325</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.5953000000000001</v>
+        <v>1.4202</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.246</v>
+        <v>1.198</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.375</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.215</v>
+        <v>1.1175</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.6879999999999999</v>
+        <v>2.88</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.3876</v>
+        <v>0.862</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.297</v>
+        <v>1.78</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.06</v>
+        <v>3.06</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.297</v>
+        <v>1.78</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.54</v>
+        <v>3.38</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.5625</v>
+        <v>2.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.05556</v>
+        <v>0.08333</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.2515</v>
+        <v>0.7124</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.03007</v>
+        <v>0.04511</v>
       </c>
       <c r="AN22" t="n">
-        <v>0.01389</v>
+        <v>0.02083</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.05556</v>
+        <v>0.08333</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.50236</v>
+        <v>2.40978</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.3197</v>
+        <v>0.7399</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.05556</v>
+        <v>0.08333</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.25118</v>
+        <v>1.20489</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.28125</v>
+        <v>1.25</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.54</v>
+        <v>3.38</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.5625</v>
+        <v>2.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.504</v>
+        <v>1.727</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.5625</v>
+        <v>2.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.755</v>
+        <v>1.71</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.28125</v>
+        <v>1.25</v>
       </c>
       <c r="BA22" t="n">
-        <v>0.28125</v>
+        <v>1.25</v>
       </c>
       <c r="BB22" t="n">
-        <v>0.16188</v>
+        <v>0.72119</v>
       </c>
       <c r="BC22" t="n">
-        <v>0.16188</v>
+        <v>0.72119</v>
       </c>
       <c r="BD22" t="n">
-        <v>0.32426</v>
+        <v>1.44288</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>6500-L-06-06-FG</t>
+          <t>6500-32-32-FG</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 9/16-18 JIC x 9/16-18 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 2 1/2-12 JIC x 2 1/2-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>9/16-18 JIC</t>
+          <t>2 1/2-12 JIC</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>9/16-18 (female 37deg JIC swivel)</t>
+          <t>2 1/2-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
@@ -5281,49 +5281,49 @@
       </c>
       <c r="BK22" t="inlineStr">
         <is>
-          <t>OMi WebsitePartsInfo2026.xlsx Items row 1937 (OMi first, user decision 2026-09-25): M = L 1, M9 = M 2 (crossing to the swivel-nut face), M12 = M 1 (crossing to the nose tip), Y = Hex Flat, CHEX = Nut Hex 1, D1 / D2 = Side 1 / Side 2 ID - column meaning from the Brennan TFA catalog p34 drawing letters (M / M6 / M4 / Y FLATS / C HEX / B1 / B2 DRILL, OMi = catalog 5/5); OMi and Brennan are ONE source -&gt; ASSUMED; male JIC end VERIFIED (MS33656J) | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-L-06-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): the forged swivel hex arm runs on to the swivel end of the same size (BRENNAN_6500-L-08-08-FG; its length through the swivel end-library constant SW2_BODYS); the sizes of the part are OMi's | FOLD: 6500-L fold: the extra length is the forged swivel hex arm, the swivel end is the 6500 one of the same size (Brennan 6500-L-08-08-FG STEP, tools/measure/swiv.py + elbow90.py: swivel end = SWIV_MEAS[8], arm 0..1.925 continuous; measured at -08 only, ASSUMED for the other sizes) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(OMi Hex Flat (Y), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = OMi Nut Hex 1 (CHEX) over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at OMi M 1 Size (M12), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = OMi M 2 Size (M9, crossing to the nut face), nose tip at OMi M 1 Size (M12, crossing to the nose tip); each leg bore runs from its face to the axis crossing</t>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-L-06-06 dims are NOT assumed; confirm before modelling | FOLDS 2026-10-02: filled from OMi Items row 1937; Brennan TFA catalog p34 (same source) differs only in the last printed digit (the catalog cuts OMi M 1 to 2 decimals, QA_Log #158; 9/16 = 0.5625 printed 0.562 / 0.563): M12 OMi 2.165 vs catalog 2.16 | 6500-L row folded into the 6500 master: Brennan 6500-L-08-08-FG STEP (pilot) = 6500-08-08-FG with the forged swivel hex arm 1.430 longer (Q-NEW-FOLD-6500L, 2026-10-02) | hex A/F raised from OMi Hex Flat 0.562 to 0.5625 (JIC thread major; 2603HX rule)</t>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs)</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>6500-L-06-06-FG</t>
+          <t>6500-32-32-FG</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6500-L-08-08-FG</t>
+          <t>6500-L-04-04-FG</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.25</v>
+        <v>0.89</v>
       </c>
       <c r="C23" t="n">
-        <v>0.375</v>
+        <v>0.219</v>
       </c>
       <c r="D23" t="n">
-        <v>0.375</v>
+        <v>0.21875</v>
       </c>
       <c r="E23" t="n">
-        <v>0.094</v>
+        <v>0.075</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2837</v>
+        <v>0.2608</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3295</v>
+        <v>0.182</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0984</v>
+        <v>0.0795</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1546</v>
+        <v>0.1135</v>
       </c>
       <c r="J23" t="n">
         <v>60</v>
@@ -5332,148 +5332,148 @@
         <v>37</v>
       </c>
       <c r="L23" t="n">
-        <v>2.81</v>
+        <v>2.16</v>
       </c>
       <c r="M23" t="n">
-        <v>0.375</v>
+        <v>0.219</v>
       </c>
       <c r="N23" t="n">
-        <v>0.885</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>0.292</v>
+        <v>0.1465</v>
       </c>
       <c r="P23" t="n">
-        <v>0.827</v>
+        <v>0.649</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.4108</v>
+        <v>0.2574</v>
       </c>
       <c r="R23" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4361</v>
+        <v>0.2796</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4499</v>
+        <v>0.3268</v>
       </c>
       <c r="U23" t="n">
-        <v>0.50518</v>
+        <v>0.32505</v>
       </c>
       <c r="V23" t="n">
-        <v>0.375</v>
+        <v>0.21875</v>
       </c>
       <c r="W23" t="n">
-        <v>0.34117</v>
+        <v>0.19169</v>
       </c>
       <c r="X23" t="n">
-        <v>0.3283</v>
+        <v>0.264</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.3925</v>
+        <v>0.235</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.6723</v>
+        <v>0.5243</v>
       </c>
       <c r="AA23" t="n">
+        <v>0.1845</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0.02706</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.2867</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0.19169</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="AW23" t="n">
         <v>0.34</v>
       </c>
-      <c r="AB23" t="n">
-        <v>0.422</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0.2825</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0.4499</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0.391</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0.391</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0.2837</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>0.03383</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>0.01562</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0.6823399999999999</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0.3567</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0.34117</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0.593</v>
-      </c>
       <c r="AX23" t="n">
-        <v>0.75</v>
+        <v>0.438</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.925</v>
+        <v>1.475</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.375</v>
+        <v>0.219</v>
       </c>
       <c r="BA23" t="n">
-        <v>0.375</v>
+        <v>0.219</v>
       </c>
       <c r="BB23" t="n">
-        <v>0.21601</v>
+        <v>0.12594</v>
       </c>
       <c r="BC23" t="n">
-        <v>0.21601</v>
+        <v>0.12594</v>
       </c>
       <c r="BD23" t="n">
-        <v>0.43251</v>
+        <v>0.25238</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>6500-L-08-08-FG</t>
+          <t>6500-L-04-04-FG</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 3/4-16 JIC x 3/4-16 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 7/16-20 JIC x 7/16-20 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>3/4-16 JIC</t>
+          <t>7/16-20 JIC</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>3/4-16 (female 37deg JIC swivel)</t>
+          <t>7/16-20 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
@@ -5498,49 +5498,49 @@
       </c>
       <c r="BK23" t="inlineStr">
         <is>
-          <t>OMi WebsitePartsInfo2026.xlsx Items row 1938 (OMi first, user decision 2026-09-25): M = L 1, M9 = M 2 (crossing to the swivel-nut face), M12 = M 1 (crossing to the nose tip), Y = Hex Flat, CHEX = Nut Hex 1, D1 / D2 = Side 1 / Side 2 ID - column meaning from the Brennan TFA catalog p34 drawing letters (M / M6 / M4 / Y FLATS / C HEX / B1 / B2 DRILL, OMi = catalog 5/5); OMi and Brennan are ONE source -&gt; ASSUMED; male JIC end VERIFIED (MS33656J) | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-L-08-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): the forged swivel hex arm runs on to the swivel end of the same size (BRENNAN_6500-L-08-08-FG; its length through the swivel end-library constant SW2_BODYS); the sizes of the part are OMi's | FOLD: 6500-L fold: the extra length is the forged swivel hex arm, the swivel end is the 6500 one of the same size (Brennan 6500-L-08-08-FG STEP, tools/measure/swiv.py + elbow90.py: swivel end = SWIV_MEAS[8], arm 0..1.925 continuous; measured at -08 only, ASSUMED for the other sizes) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(OMi Hex Flat (Y), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = OMi Nut Hex 1 (CHEX) over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at OMi M 1 Size (M12), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = OMi M 2 Size (M9, crossing to the nut face), nose tip at OMi M 1 Size (M12, crossing to the nose tip); each leg bore runs from its face to the axis crossing</t>
+          <t>OMi WebsitePartsInfo2026.xlsx Items row 1936 (OMi first, user decision 2026-09-25): M = L 1, M9 = M 2 (crossing to the swivel-nut face), M12 = M 1 (crossing to the nose tip), Y = Hex Flat, CHEX = Nut Hex 1, D1 / D2 = Side 1 / Side 2 ID - column meaning from the Brennan TFA catalog p34 drawing letters (M / M6 / M4 / Y FLATS / C HEX / B1 / B2 DRILL, OMi = catalog 5/5); OMi and Brennan are ONE source -&gt; ASSUMED; male JIC end VERIFIED (MS33656J) | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-L-04-04 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): the forged swivel hex arm runs on to the swivel end of the same size (BRENNAN_6500-L-08-08-FG; its length through the swivel end-library constant SW2_BODYS); the sizes of the part are OMi's | FOLD: 6500-L fold: the extra length is the forged swivel hex arm, the swivel end is the 6500 one of the same size (Brennan 6500-L-08-08-FG STEP, tools/measure/swiv.py + elbow90.py: swivel end = SWIV_MEAS[8], arm 0..1.925 continuous; measured at -08 only, ASSUMED for the other sizes) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(OMi Hex Flat (Y), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = OMi Nut Hex 1 (CHEX) over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at OMi M 1 Size (M12), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = OMi M 2 Size (M9, crossing to the nut face), nose tip at OMi M 1 Size (M12, crossing to the nose tip); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-L-08-08 dims are NOT assumed; confirm before modelling | FOLDS 2026-10-02: filled from OMi Items row 1938; Brennan TFA catalog p34 (same source) differs only in the last printed digit (the catalog cuts OMi M 1 to 2 decimals, QA_Log #158; 9/16 = 0.5625 printed 0.562 / 0.563): M12 OMi 2.388 vs catalog 2.38; Brennan 6500-L-08-08-FG STEP (pilot, elbow90.py + swiv.py): M 1.2501; M9 2.8101; M12 2.3801; Y 0.75; CHEX 0.875; D1 0.391; D2 0.391 - equal to OMi except the nose tip M12 (STEP 2.3801 = nut face 2.8101 - 0.43; OMi 2.388, +0.008, the same offset as OMi / Air-Way 0.96 vs the 6500-08-08-FG STEP 0.95) - built to OMi | 6500-L row folded into the 6500 master: Brennan 6500-L-08-08-FG STEP (pilot) = 6500-08-08-FG with the forged swivel hex arm 1.430 longer (Q-NEW-FOLD-6500L, 2026-10-02)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-L-04-04 dims are NOT assumed; confirm before modelling | FOLDS 2026-10-02: filled from OMi Items row 1936; Brennan TFA catalog p34 (same source) differs only in the last printed digit (the catalog cuts OMi M 1 to 2 decimals, QA_Log #158; 9/16 = 0.5625 printed 0.562 / 0.563): M12 OMi 1.816 vs catalog 1.81; CHEX OMi 0.563 vs catalog 0.562 | 6500-L row folded into the 6500 master: Brennan 6500-L-08-08-FG STEP (pilot) = 6500-08-08-FG with the forged swivel hex arm 1.430 longer (Q-NEW-FOLD-6500L, 2026-10-02)</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>6500-L-08-08-FG</t>
+          <t>6500-L-04-04-FG</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6500-L-12-12-FG</t>
+          <t>6500-L-06-06-FG</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.66</v>
+        <v>1.06</v>
       </c>
       <c r="C24" t="n">
-        <v>0.53125</v>
+        <v>0.28125</v>
       </c>
       <c r="D24" t="n">
-        <v>0.53125</v>
+        <v>0.28125</v>
       </c>
       <c r="E24" t="n">
-        <v>0.125</v>
+        <v>0.083</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3895</v>
+        <v>0.2515</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4715</v>
+        <v>0.2405</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1299</v>
+        <v>0.0898</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1851</v>
+        <v>0.1082</v>
       </c>
       <c r="J24" t="n">
         <v>60</v>
@@ -5549,148 +5549,148 @@
         <v>37</v>
       </c>
       <c r="L24" t="n">
-        <v>4.3</v>
+        <v>2.54</v>
       </c>
       <c r="M24" t="n">
-        <v>0.53125</v>
+        <v>0.28125</v>
       </c>
       <c r="N24" t="n">
-        <v>1.089</v>
+        <v>0.785</v>
       </c>
       <c r="O24" t="n">
-        <v>0.417</v>
+        <v>0.206</v>
       </c>
       <c r="P24" t="n">
-        <v>1.047</v>
+        <v>0.735</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.5928</v>
+        <v>0.3224</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2</v>
+        <v>0.145</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6237</v>
+        <v>0.3428</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5998</v>
+        <v>0.3876</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.39722</v>
       </c>
       <c r="V24" t="n">
-        <v>0.53125</v>
+        <v>0.28125</v>
       </c>
       <c r="W24" t="n">
-        <v>0.48614</v>
+        <v>0.25118</v>
       </c>
       <c r="X24" t="n">
-        <v>0.4472</v>
+        <v>0.2945</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.549</v>
+        <v>0.2925</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.8623</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.481</v>
+        <v>0.246</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.375</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.4225</v>
+        <v>0.215</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.25</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.5998</v>
+        <v>0.3876</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.609</v>
+        <v>0.297</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.66</v>
+        <v>1.06</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.609</v>
+        <v>0.297</v>
       </c>
       <c r="AI24" t="n">
-        <v>4.3</v>
+        <v>2.54</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.0625</v>
+        <v>0.5625</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.3895</v>
+        <v>0.2515</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.04511</v>
+        <v>0.03007</v>
       </c>
       <c r="AN24" t="n">
-        <v>0.02083</v>
+        <v>0.01389</v>
       </c>
       <c r="AO24" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.97228</v>
+        <v>0.50236</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.4851</v>
+        <v>0.3197</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.48614</v>
+        <v>0.25118</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.53125</v>
+        <v>0.28125</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.3</v>
+        <v>2.54</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.0625</v>
+        <v>0.5625</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.796</v>
+        <v>0.504</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.0625</v>
+        <v>0.5625</v>
       </c>
       <c r="AY24" t="n">
-        <v>3.211</v>
+        <v>1.755</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.53125</v>
+        <v>0.28125</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.53125</v>
+        <v>0.28125</v>
       </c>
       <c r="BB24" t="n">
-        <v>0.30622</v>
+        <v>0.16188</v>
       </c>
       <c r="BC24" t="n">
-        <v>0.30622</v>
+        <v>0.16188</v>
       </c>
       <c r="BD24" t="n">
-        <v>0.61293</v>
+        <v>0.32426</v>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
-          <t>6500-L-12-12-FG</t>
+          <t>6500-L-06-06-FG</t>
         </is>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>90 deg Female Swivel Elbow, 1 1/16-12 JIC x 1 1/16-12 (female 37deg JIC swivel)</t>
+          <t>90 deg Female Swivel Elbow, 9/16-18 JIC x 9/16-18 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>1 1/16-12 JIC</t>
+          <t>9/16-18 JIC</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female 37deg JIC swivel)</t>
+          <t>9/16-18 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
@@ -5715,49 +5715,49 @@
       </c>
       <c r="BK24" t="inlineStr">
         <is>
-          <t>OMi WebsitePartsInfo2026.xlsx Items row 1939 (OMi first, user decision 2026-09-25): M = L 1, M9 = M 2 (crossing to the swivel-nut face), M12 = M 1 (crossing to the nose tip), Y = Hex Flat, CHEX = Nut Hex 1, D1 / D2 = Side 1 / Side 2 ID - column meaning from the Brennan TFA catalog p34 drawing letters (M / M6 / M4 / Y FLATS / C HEX / B1 / B2 DRILL, OMi = catalog 5/5); OMi and Brennan are ONE source -&gt; ASSUMED; male JIC end VERIFIED (MS33656J) | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-L-12-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): the forged swivel hex arm runs on to the swivel end of the same size (BRENNAN_6500-L-08-08-FG; its length through the swivel end-library constant SW2_BODYS); the sizes of the part are OMi's | FOLD: 6500-L fold: the extra length is the forged swivel hex arm, the swivel end is the 6500 one of the same size (Brennan 6500-L-08-08-FG STEP, tools/measure/swiv.py + elbow90.py: swivel end = SWIV_MEAS[8], arm 0..1.925 continuous; measured at -08 only, ASSUMED for the other sizes) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(OMi Hex Flat (Y), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = OMi Nut Hex 1 (CHEX) over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at OMi M 1 Size (M12), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = OMi M 2 Size (M9, crossing to the nut face), nose tip at OMi M 1 Size (M12, crossing to the nose tip); each leg bore runs from its face to the axis crossing</t>
+          <t>OMi WebsitePartsInfo2026.xlsx Items row 1937 (OMi first, user decision 2026-09-25): M = L 1, M9 = M 2 (crossing to the swivel-nut face), M12 = M 1 (crossing to the nose tip), Y = Hex Flat, CHEX = Nut Hex 1, D1 / D2 = Side 1 / Side 2 ID - column meaning from the Brennan TFA catalog p34 drawing letters (M / M6 / M4 / Y FLATS / C HEX / B1 / B2 DRILL, OMi = catalog 5/5); OMi and Brennan are ONE source -&gt; ASSUMED; male JIC end VERIFIED (MS33656J) | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-L-06-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): the forged swivel hex arm runs on to the swivel end of the same size (BRENNAN_6500-L-08-08-FG; its length through the swivel end-library constant SW2_BODYS); the sizes of the part are OMi's | FOLD: 6500-L fold: the extra length is the forged swivel hex arm, the swivel end is the 6500 one of the same size (Brennan 6500-L-08-08-FG STEP, tools/measure/swiv.py + elbow90.py: swivel end = SWIV_MEAS[8], arm 0..1.925 continuous; measured at -08 only, ASSUMED for the other sizes) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(OMi Hex Flat (Y), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = OMi Nut Hex 1 (CHEX) over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at OMi M 1 Size (M12), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = OMi M 2 Size (M9, crossing to the nut face), nose tip at OMi M 1 Size (M12, crossing to the nose tip); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-L-12-12 dims are NOT assumed; confirm before modelling | FOLDS 2026-10-02: filled from OMi Items row 1939; Brennan TFA catalog p34 (same source) differs only in the last printed digit (the catalog cuts OMi M 1 to 2 decimals, QA_Log #158; 9/16 = 0.5625 printed 0.562 / 0.563): M12 OMi 3.738 vs catalog 3.73 | 6500-L row folded into the 6500 master: Brennan 6500-L-08-08-FG STEP (pilot) = 6500-08-08-FG with the forged swivel hex arm 1.430 longer (Q-NEW-FOLD-6500L, 2026-10-02) | hex A/F raised from OMi Hex Flat 1.062 to 1.0625 (JIC thread major; 2603HX rule)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-L-06-06 dims are NOT assumed; confirm before modelling | FOLDS 2026-10-02: filled from OMi Items row 1937; Brennan TFA catalog p34 (same source) differs only in the last printed digit (the catalog cuts OMi M 1 to 2 decimals, QA_Log #158; 9/16 = 0.5625 printed 0.562 / 0.563): M12 OMi 2.165 vs catalog 2.16 | 6500-L row folded into the 6500 master: Brennan 6500-L-08-08-FG STEP (pilot) = 6500-08-08-FG with the forged swivel hex arm 1.430 longer (Q-NEW-FOLD-6500L, 2026-10-02) | hex A/F raised from OMi Hex Flat 0.562 to 0.5625 (JIC thread major; 2603HX rule)</t>
         </is>
       </c>
       <c r="BM24" t="inlineStr">
         <is>
-          <t>6500-L-12-12-FG</t>
+          <t>6500-L-06-06-FG</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6500-L-16-16-FG</t>
+          <t>6500-L-08-08-FG</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="C25" t="n">
-        <v>0.65625</v>
+        <v>0.375</v>
       </c>
       <c r="D25" t="n">
-        <v>0.65625</v>
+        <v>0.375</v>
       </c>
       <c r="E25" t="n">
-        <v>0.125</v>
+        <v>0.094</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4365</v>
+        <v>0.2837</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5965</v>
+        <v>0.3295</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1292</v>
+        <v>0.0984</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1858</v>
+        <v>0.1546</v>
       </c>
       <c r="J25" t="n">
         <v>60</v>
@@ -5766,181 +5766,615 @@
         <v>37</v>
       </c>
       <c r="L25" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.4108</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.4361</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.50518</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.6723</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.2825</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0.6823399999999999</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.925</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0.43251</v>
+      </c>
+      <c r="BE25" t="inlineStr">
+        <is>
+          <t>6500-L-08-08-FG</t>
+        </is>
+      </c>
+      <c r="BF25" t="inlineStr">
+        <is>
+          <t>90 deg Female Swivel Elbow, 3/4-16 JIC x 3/4-16 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BG25" t="inlineStr">
+        <is>
+          <t>6500</t>
+        </is>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>3/4-16 JIC</t>
+        </is>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>3/4-16 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BJ25" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BK25" t="inlineStr">
+        <is>
+          <t>OMi WebsitePartsInfo2026.xlsx Items row 1938 (OMi first, user decision 2026-09-25): M = L 1, M9 = M 2 (crossing to the swivel-nut face), M12 = M 1 (crossing to the nose tip), Y = Hex Flat, CHEX = Nut Hex 1, D1 / D2 = Side 1 / Side 2 ID - column meaning from the Brennan TFA catalog p34 drawing letters (M / M6 / M4 / Y FLATS / C HEX / B1 / B2 DRILL, OMi = catalog 5/5); OMi and Brennan are ONE source -&gt; ASSUMED; male JIC end VERIFIED (MS33656J) | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-L-08-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): the forged swivel hex arm runs on to the swivel end of the same size (BRENNAN_6500-L-08-08-FG; its length through the swivel end-library constant SW2_BODYS); the sizes of the part are OMi's | FOLD: 6500-L fold: the extra length is the forged swivel hex arm, the swivel end is the 6500 one of the same size (Brennan 6500-L-08-08-FG STEP, tools/measure/swiv.py + elbow90.py: swivel end = SWIV_MEAS[8], arm 0..1.925 continuous; measured at -08 only, ASSUMED for the other sizes) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(OMi Hex Flat (Y), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = OMi Nut Hex 1 (CHEX) over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at OMi M 1 Size (M12), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = OMi M 2 Size (M9, crossing to the nut face), nose tip at OMi M 1 Size (M12, crossing to the nose tip); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BL25" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-L-08-08 dims are NOT assumed; confirm before modelling | FOLDS 2026-10-02: filled from OMi Items row 1938; Brennan TFA catalog p34 (same source) differs only in the last printed digit (the catalog cuts OMi M 1 to 2 decimals, QA_Log #158; 9/16 = 0.5625 printed 0.562 / 0.563): M12 OMi 2.388 vs catalog 2.38; Brennan 6500-L-08-08-FG STEP (pilot, elbow90.py + swiv.py): M 1.2501; M9 2.8101; M12 2.3801; Y 0.75; CHEX 0.875; D1 0.391; D2 0.391 - equal to OMi except the nose tip M12 (STEP 2.3801 = nut face 2.8101 - 0.43; OMi 2.388, +0.008, the same offset as OMi / Air-Way 0.96 vs the 6500-08-08-FG STEP 0.95) - built to OMi | 6500-L row folded into the 6500 master: Brennan 6500-L-08-08-FG STEP (pilot) = 6500-08-08-FG with the forged swivel hex arm 1.430 longer (Q-NEW-FOLD-6500L, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="BM25" t="inlineStr">
+        <is>
+          <t>6500-L-08-08-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>6500-L-12-12-FG</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.4715</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="J26" t="n">
+        <v>60</v>
+      </c>
+      <c r="K26" t="n">
+        <v>37</v>
+      </c>
+      <c r="L26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.5928</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.6237</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.7216900000000001</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.4472</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.8623</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.4225</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0.97228</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0.4851</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>3.211</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0.61293</v>
+      </c>
+      <c r="BE26" t="inlineStr">
+        <is>
+          <t>6500-L-12-12-FG</t>
+        </is>
+      </c>
+      <c r="BF26" t="inlineStr">
+        <is>
+          <t>90 deg Female Swivel Elbow, 1 1/16-12 JIC x 1 1/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BG26" t="inlineStr">
+        <is>
+          <t>6500</t>
+        </is>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>1 1/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BJ26" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BK26" t="inlineStr">
+        <is>
+          <t>OMi WebsitePartsInfo2026.xlsx Items row 1939 (OMi first, user decision 2026-09-25): M = L 1, M9 = M 2 (crossing to the swivel-nut face), M12 = M 1 (crossing to the nose tip), Y = Hex Flat, CHEX = Nut Hex 1, D1 / D2 = Side 1 / Side 2 ID - column meaning from the Brennan TFA catalog p34 drawing letters (M / M6 / M4 / Y FLATS / C HEX / B1 / B2 DRILL, OMi = catalog 5/5); OMi and Brennan are ONE source -&gt; ASSUMED; male JIC end VERIFIED (MS33656J) | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-L-12-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): the forged swivel hex arm runs on to the swivel end of the same size (BRENNAN_6500-L-08-08-FG; its length through the swivel end-library constant SW2_BODYS); the sizes of the part are OMi's | FOLD: 6500-L fold: the extra length is the forged swivel hex arm, the swivel end is the 6500 one of the same size (Brennan 6500-L-08-08-FG STEP, tools/measure/swiv.py + elbow90.py: swivel end = SWIV_MEAS[8], arm 0..1.925 continuous; measured at -08 only, ASSUMED for the other sizes) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(OMi Hex Flat (Y), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = OMi Nut Hex 1 (CHEX) over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at OMi M 1 Size (M12), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = OMi M 2 Size (M9, crossing to the nut face), nose tip at OMi M 1 Size (M12, crossing to the nose tip); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BL26" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-L-12-12 dims are NOT assumed; confirm before modelling | FOLDS 2026-10-02: filled from OMi Items row 1939; Brennan TFA catalog p34 (same source) differs only in the last printed digit (the catalog cuts OMi M 1 to 2 decimals, QA_Log #158; 9/16 = 0.5625 printed 0.562 / 0.563): M12 OMi 3.738 vs catalog 3.73 | 6500-L row folded into the 6500 master: Brennan 6500-L-08-08-FG STEP (pilot) = 6500-08-08-FG with the forged swivel hex arm 1.430 longer (Q-NEW-FOLD-6500L, 2026-10-02) | hex A/F raised from OMi Hex Flat 1.062 to 1.0625 (JIC thread major; 2603HX rule)</t>
+        </is>
+      </c>
+      <c r="BM26" t="inlineStr">
+        <is>
+          <t>6500-L-12-12-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>6500-L-16-16-FG</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="J27" t="n">
+        <v>60</v>
+      </c>
+      <c r="K27" t="n">
+        <v>37</v>
+      </c>
+      <c r="L27" t="n">
         <v>5</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M27" t="n">
         <v>0.65625</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N27" t="n">
         <v>1.175</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O27" t="n">
         <v>0.5485</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P27" t="n">
         <v>1.139</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q27" t="n">
         <v>0.727</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R27" t="n">
         <v>0.23</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S27" t="n">
         <v>0.749</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T27" t="n">
         <v>0.6564</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U27" t="n">
         <v>0.86603</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V27" t="n">
         <v>0.65625</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W27" t="n">
         <v>0.61114</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X27" t="n">
         <v>0.4873</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="Y27" t="n">
         <v>0.665</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="Z27" t="n">
         <v>0.9544</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AA27" t="n">
         <v>0.604</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AB27" t="n">
         <v>0.594</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AC27" t="n">
         <v>0.5475</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AD27" t="n">
         <v>1.5</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AE27" t="n">
         <v>0.6564</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AF27" t="n">
         <v>0.844</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AG27" t="n">
         <v>1.81</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AH27" t="n">
         <v>0.844</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AI27" t="n">
         <v>5</v>
       </c>
-      <c r="AJ25" t="n">
+      <c r="AJ27" t="n">
         <v>1.3125</v>
       </c>
-      <c r="AK25" t="n">
+      <c r="AK27" t="n">
         <v>0.08333</v>
       </c>
-      <c r="AL25" t="n">
+      <c r="AL27" t="n">
         <v>0.4365</v>
       </c>
-      <c r="AM25" t="n">
+      <c r="AM27" t="n">
         <v>0.04511</v>
       </c>
-      <c r="AN25" t="n">
+      <c r="AN27" t="n">
         <v>0.02083</v>
       </c>
-      <c r="AO25" t="n">
+      <c r="AO27" t="n">
         <v>0.08333</v>
       </c>
-      <c r="AP25" t="n">
+      <c r="AP27" t="n">
         <v>1.22228</v>
       </c>
-      <c r="AQ25" t="n">
+      <c r="AQ27" t="n">
         <v>0.5252</v>
       </c>
-      <c r="AR25" t="n">
+      <c r="AR27" t="n">
         <v>0.08333</v>
       </c>
-      <c r="AS25" t="n">
+      <c r="AS27" t="n">
         <v>0.61114</v>
       </c>
-      <c r="AT25" t="n">
+      <c r="AT27" t="n">
         <v>0.65625</v>
       </c>
-      <c r="AU25" t="n">
+      <c r="AU27" t="n">
         <v>5</v>
       </c>
-      <c r="AV25" t="n">
+      <c r="AV27" t="n">
         <v>1.3125</v>
       </c>
-      <c r="AW25" t="n">
+      <c r="AW27" t="n">
         <v>0.899</v>
       </c>
-      <c r="AX25" t="n">
+      <c r="AX27" t="n">
         <v>1.3125</v>
       </c>
-      <c r="AY25" t="n">
+      <c r="AY27" t="n">
         <v>3.825</v>
       </c>
-      <c r="AZ25" t="n">
+      <c r="AZ27" t="n">
         <v>0.65625</v>
       </c>
-      <c r="BA25" t="n">
+      <c r="BA27" t="n">
         <v>0.65625</v>
       </c>
-      <c r="BB25" t="n">
+      <c r="BB27" t="n">
         <v>0.37839</v>
       </c>
-      <c r="BC25" t="n">
+      <c r="BC27" t="n">
         <v>0.37839</v>
       </c>
-      <c r="BD25" t="n">
+      <c r="BD27" t="n">
         <v>0.75727</v>
       </c>
-      <c r="BE25" t="inlineStr">
+      <c r="BE27" t="inlineStr">
         <is>
           <t>6500-L-16-16-FG</t>
         </is>
       </c>
-      <c r="BF25" t="inlineStr">
+      <c r="BF27" t="inlineStr">
         <is>
           <t>90 deg Female Swivel Elbow, 1 5/16-12 JIC x 1 5/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
-      <c r="BG25" t="inlineStr">
+      <c r="BG27" t="inlineStr">
         <is>
           <t>6500</t>
         </is>
       </c>
-      <c r="BH25" t="inlineStr">
+      <c r="BH27" t="inlineStr">
         <is>
           <t>1 5/16-12 JIC</t>
         </is>
       </c>
-      <c r="BI25" t="inlineStr">
+      <c r="BI27" t="inlineStr">
         <is>
           <t>1 5/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
-      <c r="BJ25" t="inlineStr">
+      <c r="BJ27" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="BK25" t="inlineStr">
+      <c r="BK27" t="inlineStr">
         <is>
           <t>OMi WebsitePartsInfo2026.xlsx Items row 1940 (OMi first, user decision 2026-09-25): M = L 1, M9 = M 2 (crossing to the swivel-nut face), M12 = M 1 (crossing to the nose tip), Y = Hex Flat, CHEX = Nut Hex 1, D1 / D2 = Side 1 / Side 2 ID - column meaning from the Brennan TFA catalog p34 drawing letters (M / M6 / M4 / Y FLATS / C HEX / B1 / B2 DRILL, OMi = catalog 5/5); OMi and Brennan are ONE source -&gt; ASSUMED; male JIC end VERIFIED (MS33656J) | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-L-16-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): the forged swivel hex arm runs on to the swivel end of the same size (BRENNAN_6500-L-08-08-FG; its length through the swivel end-library constant SW2_BODYS); the sizes of the part are OMi's | FOLD: 6500-L fold: the extra length is the forged swivel hex arm, the swivel end is the 6500 one of the same size (Brennan 6500-L-08-08-FG STEP, tools/measure/swiv.py + elbow90.py: swivel end = SWIV_MEAS[8], arm 0..1.925 continuous; measured at -08 only, ASSUMED for the other sizes) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(OMi Hex Flat (Y), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = OMi Nut Hex 1 (CHEX) over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at OMi M 1 Size (M12), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = OMi M 2 Size (M9, crossing to the nut face), nose tip at OMi M 1 Size (M12, crossing to the nose tip); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="BL25" t="inlineStr">
+      <c r="BL27" t="inlineStr">
         <is>
           <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-L-16-16 dims are NOT assumed; confirm before modelling | FOLDS 2026-10-02: filled from OMi Items row 1940; Brennan TFA catalog p34 (same source) differs only in the last printed digit (the catalog cuts OMi M 1 to 2 decimals, QA_Log #158; 9/16 = 0.5625 printed 0.562 / 0.563): M12 OMi 4.406 vs catalog 4.40 | 6500-L row folded into the 6500 master: Brennan 6500-L-08-08-FG STEP (pilot) = 6500-08-08-FG with the forged swivel hex arm 1.430 longer (Q-NEW-FOLD-6500L, 2026-10-02) | hex A/F raised from OMi Hex Flat 1.312 to 1.3125 (JIC thread major; 2603HX rule)</t>
         </is>
       </c>
-      <c r="BM25" t="inlineStr">
+      <c r="BM27" t="inlineStr">
         <is>
           <t>6500-L-16-16-FG</t>
         </is>

--- a/04_DESIGN_TABLES/DesignTable_6500_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6500_SW2.xlsx
@@ -823,7 +823,7 @@
         <v>0.481</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AC2" t="n">
         <v>0.4225</v>
@@ -941,12 +941,12 @@
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); LEG_M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1926 = 1.18 (table had 1.19) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); LEG_M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1926 = 1.18 (table had 1.19) [user 2026-10-18 A19]; LEG_M10@DRIVE: Air-Way 1.19 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.18) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | A19 (user 2026-10-18, group 2 settled): LEG_M10@DRIVE 1.19 -&gt; OMi 1.18 (Items!N1926, M113) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs) | hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule)</t>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | A19 (user 2026-10-18, group 2 settled): LEG_M10@DRIVE 1.19 -&gt; OMi 1.18 (Items!N1926, M113) | 2026-10-20 Air-Way first: LEG_M10@DRIVE OMi/Brennan 1.18 -&gt; Air-Way 1.19 | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs) | hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule)</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1474,7 +1474,7 @@
         <v>0.218</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="AC5" t="n">
         <v>0.175</v>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); LEG_M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1914 = 0.68 (table had 0.69) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); LEG_M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1914 = 0.68 (table had 0.69) [user 2026-10-18 A19]; LEG_M10@DRIVE: Air-Way 0.69 (log (no Air-Way raw extract in the repo); OMi file / Brennan 0.68) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | A19 (user 2026-10-18, group 2 settled): LEG_M10@DRIVE 0.69 -&gt; OMi 0.68 (Items!N1914, M113) | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs) | leg 2: the corner puck (radius 0.323) reaches 0.009 past the swivel body face (0.314) but stays inside the neck (max 0.077 off the axis vs neck radius 0.178) - as on the Brennan 6502-08-08-FG / 1503-08-08-FG forgings; leg 2 hex arm 0.314 barely clears the corner puck (radius 0.323)</t>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | A19 (user 2026-10-18, group 2 settled): LEG_M10@DRIVE 0.69 -&gt; OMi 0.68 (Items!N1914, M113) | 2026-10-20 Air-Way first: LEG_M10@DRIVE OMi/Brennan 0.68 -&gt; Air-Way 0.69 | DataStatus VERIFIED-LEGS -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs) | leg 2: the corner puck (radius 0.323) reaches 0.009 past the swivel body face (0.314) but stays inside the neck (max 0.077 off the axis vs neck radius 0.178) - as on the Brennan 6502-08-08-FG / 1503-08-08-FG forgings; leg 2 hex arm 0.314 barely clears the corner puck (radius 0.323)</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2294,7 +2294,7 @@
         <v>37</v>
       </c>
       <c r="L9" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="n">
         <v>0.375</v>
@@ -2342,7 +2342,7 @@
         <v>0.246</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="AC9" t="n">
         <v>0.215</v>
@@ -2363,7 +2363,7 @@
         <v>0.3</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AJ9" t="n">
         <v>0.75</v>
@@ -2399,7 +2399,7 @@
         <v>0.28125</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AV9" t="n">
         <v>0.75</v>
@@ -2411,7 +2411,7 @@
         <v>0.75</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.495</v>
+        <v>0.545</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.375</v>
@@ -2460,12 +2460,12 @@
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); LEG_M5@DRIVE: Air-Way 1.33 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.28) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; LEG_M10@DRIVE: Air-Way 0.95 (log (no Air-Way raw extract in the repo); OMi file / Brennan 0.91) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p034-t01: agrees on LEG_M@DRIVE, HEXB@HEX, Y@REF, D1@BORE, D2@BORE | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): LEG_M5@DRIVE 1.33 -&gt; 1.28 | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): LEG_M10@DRIVE 0.95 -&gt; 0.91 | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): $PRP@DataStatus VERIFIED -&gt; ASSUMED</t>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p034-t01: agrees on LEG_M@DRIVE, HEXB@HEX, Y@REF, D1@BORE, D2@BORE | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): LEG_M5@DRIVE 1.33 -&gt; 1.28 | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): LEG_M10@DRIVE 0.95 -&gt; 0.91 | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): $PRP@DataStatus VERIFIED -&gt; ASSUMED | 2026-10-20 Air-Way first: LEG_M5@DRIVE OMi/Brennan 1.28 -&gt; Air-Way 1.33 | 2026-10-20 Air-Way first: LEG_M10@DRIVE OMi/Brennan 0.91 -&gt; Air-Way 0.95 | DataStatus VERIFIED -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs)</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -2918,7 +2918,7 @@
         <v>1.42</v>
       </c>
       <c r="C12" t="n">
-        <v>0.531</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="D12" t="n">
         <v>0.375</v>
@@ -2948,7 +2948,7 @@
         <v>1.75</v>
       </c>
       <c r="M12" t="n">
-        <v>0.531</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="N12" t="n">
         <v>1.089</v>
@@ -3053,31 +3053,31 @@
         <v>1.75</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.062</v>
+        <v>1.13</v>
       </c>
       <c r="AW12" t="n">
         <v>0.763</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.062</v>
+        <v>1.13</v>
       </c>
       <c r="AY12" t="n">
         <v>0.661</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.531</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.531</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.30607</v>
+        <v>0.3257</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.30607</v>
+        <v>0.3257</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.61265</v>
+        <v>0.65191</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -3111,12 +3111,12 @@
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R1921 Hex Flat = 1.062 (table had 1.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R1921 Hex Flat = 1.062 (table had 1.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; Y@REF: Air-Way 1.13 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.062) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs)</t>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | 2026-10-20 Air-Way first: Y@REF OMi/Brennan 1.062 -&gt; Air-Way 1.13 | leg 2 hex arm 0.661 barely clears the corner puck (radius 0.652)</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -3644,7 +3644,7 @@
         <v>0.481</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AC15" t="n">
         <v>0.4225</v>
@@ -3762,12 +3762,12 @@
       </c>
       <c r="BK15" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); LEG_M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1924 = 1.18 (table had 1.19) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); LEG_M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1924 = 1.18 (table had 1.19) [user 2026-10-18 A19]; LEG_M10@DRIVE: Air-Way 1.19 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.18) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | A19 (user 2026-10-18, group 2 settled): LEG_M10@DRIVE 1.19 -&gt; OMi 1.18 (Items!N1924, M113)</t>
+          <t>RESOLVED 2026-09-24 for swivel dashes -04/-08/-12/-16: swivel nut, nose and 37deg seat measured on the Brennan 6500-04/-08/-12/-16-FG STEPs (was BLOCKED: female-JIC swivel nut internal geometry unpublished) | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat measured 2026-09-24 (Brennan STEPs) | A19 (user 2026-10-18, group 2 settled): LEG_M10@DRIVE 1.19 -&gt; OMi 1.18 (Items!N1924, M113) | 2026-10-20 Air-Way first: LEG_M10@DRIVE OMi/Brennan 1.18 -&gt; Air-Way 1.19</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
